--- a/rp/Excel/Effects_特效.xlsx
+++ b/rp/Excel/Effects_特效.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9015" tabRatio="500"/>
+    <workbookView windowHeight="17655" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="49">
   <si>
     <t>Int</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>0|0|0|0|0|0|1|1|1</t>
-  </si>
-  <si>
-    <t>0|0|150|0|0|0|1|1|1</t>
   </si>
   <si>
     <t>广告牌</t>
@@ -176,6 +173,9 @@
   </si>
   <si>
     <t>剪纸</t>
+  </si>
+  <si>
+    <t>0|0|150|0|0|0|1|1|1</t>
   </si>
 </sst>
 </file>
@@ -1525,10 +1525,10 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>558271</v>
+        <v>674918</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
@@ -1710,13 +1710,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="4">
         <v>57202</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -1743,13 +1743,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="4">
         <v>365194</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="4">
         <v>28451</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -1809,7 +1809,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="4">
         <v>526080</v>
@@ -1846,7 +1846,7 @@
         <v>464265</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>266517</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>266518</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         <v>266519</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -1970,7 +1970,7 @@
         <v>266520</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" s="4">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>266521</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E21" s="4">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>439411</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
@@ -2125,7 +2125,7 @@
         <v>439415</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>144093</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>326212</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E27" s="4">
         <v>0</v>
@@ -2218,7 +2218,7 @@
         <v>326224</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -2249,7 +2249,7 @@
         <v>383667</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>383676</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>386040</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E31" s="4">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>394667</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         <v>394678</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E33" s="4">
         <v>0</v>
@@ -2400,13 +2400,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C34" s="4">
         <v>220840</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>485354</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -2464,13 +2464,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C36" s="4">
         <v>220841</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -2497,13 +2497,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C37" s="4">
         <v>220842</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -2530,13 +2530,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C38" s="4">
         <v>220843</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
@@ -2563,13 +2563,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C39" s="4">
         <v>220844</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -2596,13 +2596,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C40" s="4">
         <v>220845</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
@@ -2629,13 +2629,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="4">
         <v>220846</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
@@ -2662,13 +2662,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="4">
         <v>220847</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C43" s="4">
         <v>220848</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
@@ -2728,13 +2728,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C44" s="4">
         <v>220849</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
@@ -2761,13 +2761,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C45" s="4">
         <v>220850</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -2794,13 +2794,13 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C46" s="4">
         <v>220851</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
@@ -2827,13 +2827,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C47" s="4">
         <v>220041</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E47" s="4">
         <v>0</v>
@@ -2860,13 +2860,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C48" s="4">
         <v>220469</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E48" s="4">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C49" s="4">
         <v>31645</v>
@@ -2926,7 +2926,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C50" s="4">
         <v>4366</v>
@@ -2959,7 +2959,7 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C51" s="4">
         <v>4367</v>
@@ -2992,7 +2992,7 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C52" s="4">
         <v>4368</v>
@@ -3029,7 +3029,7 @@
         <v>144084</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E53" s="4">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>144083</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E55" s="4">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C56" s="4">
         <v>32240</v>
@@ -3151,7 +3151,7 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C57" s="4">
         <v>59956</v>
@@ -3184,7 +3184,7 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C58" s="4">
         <v>73402</v>
@@ -3217,7 +3217,7 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C59" s="4">
         <v>88762</v>
@@ -3250,7 +3250,7 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C60" s="4">
         <v>88773</v>
@@ -3283,7 +3283,7 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C61" s="4">
         <v>89073</v>
@@ -3316,7 +3316,7 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C62" s="4">
         <v>89109</v>
@@ -3349,7 +3349,7 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C63" s="4">
         <v>89111</v>
@@ -3382,7 +3382,7 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C64" s="4">
         <v>89112</v>
@@ -3415,7 +3415,7 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C65" s="4">
         <v>89122</v>
@@ -3448,7 +3448,7 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C66" s="4">
         <v>113903</v>
@@ -3481,7 +3481,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C67" s="4">
         <v>113913</v>
@@ -3514,7 +3514,7 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C68" s="4">
         <v>113907</v>
@@ -3547,7 +3547,7 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C69" s="4">
         <v>119917</v>
@@ -3580,7 +3580,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C70" s="4">
         <v>130776</v>
@@ -3613,7 +3613,7 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C71" s="4">
         <v>141655</v>
@@ -3646,7 +3646,7 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C72" s="4">
         <v>141657</v>
@@ -3679,7 +3679,7 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C73" s="4">
         <v>142753</v>
@@ -3712,7 +3712,7 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C74" s="4">
         <v>142751</v>
@@ -3745,7 +3745,7 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C75" s="4">
         <v>142951</v>
@@ -3778,7 +3778,7 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C76" s="4">
         <v>156399</v>
@@ -3904,7 +3904,7 @@
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C80" s="4">
         <v>271322</v>
@@ -3937,7 +3937,7 @@
         <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C81" s="4">
         <v>311092</v>
@@ -3970,7 +3970,7 @@
         <v>78</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C82" s="4">
         <v>318586</v>
@@ -4034,7 +4034,7 @@
         <v>80</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C84" s="4">
         <v>127013</v>
@@ -4160,7 +4160,7 @@
         <v>84</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C88" s="4">
         <v>146754</v>
@@ -4193,7 +4193,7 @@
         <v>85</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C89" s="4">
         <v>144082</v>
@@ -4226,7 +4226,7 @@
         <v>86</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C90" s="4">
         <v>361275</v>
@@ -4255,11 +4255,19 @@
       <c r="U90" s="2"/>
     </row>
     <row r="91" spans="1:21">
-      <c r="A91" s="2"/>
+      <c r="A91" s="4">
+        <v>87</v>
+      </c>
       <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
+      <c r="C91" s="4">
+        <v>558271</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E91" s="4">
+        <v>0</v>
+      </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>

--- a/rp/Excel/Effects_特效.xlsx
+++ b/rp/Excel/Effects_特效.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9015" tabRatio="500"/>
+    <workbookView windowWidth="24750" windowHeight="12060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="51">
   <si>
     <t>Int</t>
   </si>
@@ -58,10 +58,13 @@
 2-FeMale</t>
   </si>
   <si>
+    <t>0|0|100|0|0|0|0.1|0.1|0.1</t>
+  </si>
+  <si>
     <t>0|0|0|0|0|0|1|1|1</t>
   </si>
   <si>
-    <t>0|0|150|0|0|0|1|1|1</t>
+    <t>0|0|100|0|0|0|0.1|0.02|0.1</t>
   </si>
   <si>
     <t>广告牌</t>
@@ -176,6 +179,9 @@
   </si>
   <si>
     <t>剪纸</t>
+  </si>
+  <si>
+    <t>0|0|150|0|0|0|1|1|1</t>
   </si>
 </sst>
 </file>
@@ -1366,7 +1372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U219"/>
+  <dimension ref="A1:U224"/>
   <sheetFormatPr defaultColWidth="12.0666666666667" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="12.0666666666667" style="1"/>
@@ -1494,7 +1500,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="4">
-        <v>556585</v>
+        <v>681318</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -1525,7 +1531,7 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>558271</v>
+        <v>687895</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
@@ -1556,10 +1562,10 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="4">
-        <v>565350</v>
+        <v>687897</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" s="4">
         <v>0</v>
@@ -1587,10 +1593,10 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="4">
-        <v>567138</v>
+        <v>687899</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
@@ -1618,10 +1624,10 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="4">
-        <v>567139</v>
+        <v>688276</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
@@ -1649,10 +1655,10 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="4">
-        <v>525387</v>
+        <v>556585</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4">
         <v>0</v>
@@ -1680,10 +1686,10 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="4">
-        <v>501310</v>
+        <v>674918</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4">
         <v>0</v>
@@ -1709,14 +1715,12 @@
       <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B12" s="2"/>
       <c r="C12" s="4">
-        <v>57202</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>12</v>
+        <v>565350</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -1742,14 +1746,12 @@
       <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="B13" s="2"/>
       <c r="C13" s="4">
-        <v>365194</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>14</v>
+        <v>567138</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
@@ -1775,14 +1777,12 @@
       <c r="A14" s="4">
         <v>10</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B14" s="2"/>
       <c r="C14" s="4">
-        <v>28451</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>16</v>
+        <v>567139</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -1808,14 +1808,12 @@
       <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="B15" s="2"/>
       <c r="C15" s="4">
-        <v>526080</v>
+        <v>525387</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -1841,12 +1839,12 @@
       <c r="A16" s="4">
         <v>12</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="2"/>
       <c r="C16" s="4">
-        <v>464265</v>
+        <v>501310</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1872,12 +1870,14 @@
       <c r="A17" s="4">
         <v>13</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C17" s="4">
-        <v>266517</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>18</v>
+        <v>57202</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
@@ -1903,12 +1903,14 @@
       <c r="A18" s="4">
         <v>14</v>
       </c>
-      <c r="B18" s="6"/>
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="C18" s="4">
-        <v>266518</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>18</v>
+        <v>365194</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -1934,12 +1936,14 @@
       <c r="A19" s="4">
         <v>15</v>
       </c>
-      <c r="B19" s="6"/>
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C19" s="4">
-        <v>266519</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>18</v>
+        <v>28451</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -1965,12 +1969,14 @@
       <c r="A20" s="4">
         <v>16</v>
       </c>
-      <c r="B20" s="6"/>
+      <c r="B20" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="C20" s="4">
-        <v>266520</v>
+        <v>526080</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E20" s="4">
         <v>0</v>
@@ -1998,10 +2004,10 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="4">
-        <v>266521</v>
+        <v>464265</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21" s="4">
         <v>0</v>
@@ -2029,7 +2035,7 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="4">
-        <v>439411</v>
+        <v>266517</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>19</v>
@@ -2060,10 +2066,10 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="4">
-        <v>484531</v>
+        <v>266518</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -2091,10 +2097,10 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="4">
-        <v>144088</v>
+        <v>266519</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -2122,10 +2128,10 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="4">
-        <v>439415</v>
+        <v>266520</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -2153,10 +2159,10 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="4">
-        <v>144093</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>21</v>
+        <v>266521</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -2184,10 +2190,10 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="4">
-        <v>326212</v>
+        <v>439411</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E27" s="4">
         <v>0</v>
@@ -2215,10 +2221,10 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="4">
-        <v>326224</v>
+        <v>484531</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -2246,10 +2252,10 @@
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="4">
-        <v>383667</v>
+        <v>144088</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -2277,10 +2283,10 @@
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="4">
-        <v>383676</v>
+        <v>439415</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
@@ -2308,9 +2314,9 @@
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="4">
-        <v>386040</v>
-      </c>
-      <c r="D31" s="2" t="s">
+        <v>144093</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E31" s="4">
@@ -2339,10 +2345,10 @@
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="4">
-        <v>394667</v>
+        <v>326212</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
@@ -2370,10 +2376,10 @@
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="4">
-        <v>394678</v>
+        <v>326224</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E33" s="4">
         <v>0</v>
@@ -2399,14 +2405,12 @@
       <c r="A34" s="4">
         <v>30</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="6"/>
+      <c r="C34" s="4">
+        <v>383667</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C34" s="4">
-        <v>220840</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -2428,16 +2432,16 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
     </row>
-    <row r="35" ht="17.25" spans="1:21">
+    <row r="35" spans="1:21">
       <c r="A35" s="4">
         <v>31</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="7">
-        <v>485354</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>25</v>
+      <c r="B35" s="6"/>
+      <c r="C35" s="4">
+        <v>383676</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -2463,14 +2467,12 @@
       <c r="A36" s="4">
         <v>32</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="6"/>
+      <c r="C36" s="4">
+        <v>386040</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C36" s="4">
-        <v>220841</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -2496,14 +2498,12 @@
       <c r="A37" s="4">
         <v>33</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="6"/>
+      <c r="C37" s="4">
+        <v>394667</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C37" s="4">
-        <v>220842</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -2529,14 +2529,12 @@
       <c r="A38" s="4">
         <v>34</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="6"/>
+      <c r="C38" s="4">
+        <v>394678</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C38" s="4">
-        <v>220843</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
@@ -2562,14 +2560,14 @@
       <c r="A39" s="4">
         <v>35</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>23</v>
+      <c r="B39" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C39" s="4">
-        <v>220844</v>
+        <v>220840</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -2591,18 +2589,16 @@
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" ht="17.25" spans="1:21">
       <c r="A40" s="4">
         <v>36</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="4">
-        <v>220845</v>
+      <c r="B40" s="2"/>
+      <c r="C40" s="7">
+        <v>485354</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
@@ -2628,14 +2624,14 @@
       <c r="A41" s="4">
         <v>37</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>23</v>
+      <c r="B41" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C41" s="4">
-        <v>220846</v>
+        <v>220841</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
@@ -2662,13 +2658,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="4">
-        <v>220847</v>
+        <v>220842</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
@@ -2694,14 +2690,14 @@
       <c r="A43" s="4">
         <v>39</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>23</v>
+      <c r="B43" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C43" s="4">
-        <v>220848</v>
+        <v>220843</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
@@ -2727,14 +2723,14 @@
       <c r="A44" s="4">
         <v>40</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>23</v>
+      <c r="B44" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C44" s="4">
-        <v>220849</v>
+        <v>220844</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
@@ -2761,13 +2757,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C45" s="4">
-        <v>220850</v>
+        <v>220845</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -2793,14 +2789,14 @@
       <c r="A46" s="4">
         <v>42</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>23</v>
+      <c r="B46" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C46" s="4">
-        <v>220851</v>
+        <v>220846</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
@@ -2826,14 +2822,14 @@
       <c r="A47" s="4">
         <v>43</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>23</v>
+      <c r="B47" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C47" s="4">
-        <v>220041</v>
+        <v>220847</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E47" s="4">
         <v>0</v>
@@ -2860,13 +2856,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C48" s="4">
-        <v>220469</v>
+        <v>220848</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E48" s="4">
         <v>0</v>
@@ -2892,14 +2888,14 @@
       <c r="A49" s="4">
         <v>45</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>26</v>
+      <c r="B49" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C49" s="4">
-        <v>31645</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>9</v>
+        <v>220849</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -2926,13 +2922,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C50" s="4">
-        <v>4366</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>9</v>
+        <v>220850</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -2959,13 +2955,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C51" s="4">
-        <v>4367</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>9</v>
+        <v>220851</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -2991,14 +2987,14 @@
       <c r="A52" s="4">
         <v>48</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>29</v>
+      <c r="B52" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C52" s="4">
-        <v>4368</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>9</v>
+        <v>220041</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -3024,12 +3020,14 @@
       <c r="A53" s="4">
         <v>49</v>
       </c>
-      <c r="B53" s="2"/>
+      <c r="B53" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C53" s="4">
-        <v>144084</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>30</v>
+        <v>220469</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E53" s="4">
         <v>0</v>
@@ -3055,12 +3053,14 @@
       <c r="A54" s="4">
         <v>50</v>
       </c>
-      <c r="B54" s="2"/>
+      <c r="B54" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C54" s="4">
-        <v>146786</v>
+        <v>31645</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E54" s="4">
         <v>0</v>
@@ -3086,12 +3086,14 @@
       <c r="A55" s="4">
         <v>51</v>
       </c>
-      <c r="B55" s="2"/>
+      <c r="B55" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C55" s="4">
-        <v>144083</v>
+        <v>4366</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E55" s="4">
         <v>0</v>
@@ -3118,13 +3120,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C56" s="4">
-        <v>32240</v>
+        <v>4367</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E56" s="4">
         <v>0</v>
@@ -3151,13 +3153,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C57" s="4">
-        <v>59956</v>
+        <v>4368</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
@@ -3183,14 +3185,12 @@
       <c r="A58" s="4">
         <v>54</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="B58" s="2"/>
       <c r="C58" s="4">
-        <v>73402</v>
+        <v>144084</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E58" s="4">
         <v>0</v>
@@ -3216,14 +3216,12 @@
       <c r="A59" s="4">
         <v>55</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="B59" s="2"/>
       <c r="C59" s="4">
-        <v>88762</v>
+        <v>146786</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E59" s="4">
         <v>0</v>
@@ -3249,14 +3247,12 @@
       <c r="A60" s="4">
         <v>56</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="B60" s="2"/>
       <c r="C60" s="4">
-        <v>88773</v>
+        <v>144083</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E60" s="4">
         <v>0</v>
@@ -3283,13 +3279,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C61" s="4">
-        <v>89073</v>
+        <v>32240</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E61" s="4">
         <v>0</v>
@@ -3316,13 +3312,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C62" s="4">
-        <v>89109</v>
+        <v>59956</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E62" s="4">
         <v>0</v>
@@ -3349,13 +3345,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C63" s="4">
-        <v>89111</v>
+        <v>73402</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E63" s="4">
         <v>0</v>
@@ -3382,13 +3378,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C64" s="4">
-        <v>89112</v>
+        <v>88762</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E64" s="4">
         <v>0</v>
@@ -3415,13 +3411,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C65" s="4">
-        <v>89122</v>
+        <v>88773</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E65" s="4">
         <v>0</v>
@@ -3448,13 +3444,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C66" s="4">
-        <v>113903</v>
+        <v>89073</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E66" s="4">
         <v>0</v>
@@ -3481,13 +3477,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C67" s="4">
-        <v>113913</v>
+        <v>89109</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E67" s="4">
         <v>0</v>
@@ -3514,13 +3510,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C68" s="4">
-        <v>113907</v>
+        <v>89111</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E68" s="4">
         <v>0</v>
@@ -3547,13 +3543,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C69" s="4">
-        <v>119917</v>
+        <v>89112</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E69" s="4">
         <v>0</v>
@@ -3580,13 +3576,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C70" s="4">
-        <v>130776</v>
+        <v>89122</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E70" s="4">
         <v>0</v>
@@ -3613,13 +3609,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C71" s="4">
-        <v>141655</v>
+        <v>113903</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E71" s="4">
         <v>0</v>
@@ -3646,13 +3642,13 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C72" s="4">
-        <v>141657</v>
+        <v>113913</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E72" s="4">
         <v>0</v>
@@ -3679,13 +3675,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C73" s="4">
-        <v>142753</v>
+        <v>113907</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E73" s="4">
         <v>0</v>
@@ -3712,13 +3708,13 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C74" s="4">
-        <v>142751</v>
+        <v>119917</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E74" s="4">
         <v>0</v>
@@ -3745,13 +3741,13 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C75" s="4">
-        <v>142951</v>
+        <v>130776</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75" s="4">
         <v>0</v>
@@ -3778,13 +3774,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C76" s="4">
-        <v>156399</v>
+        <v>141655</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" s="4">
         <v>0</v>
@@ -3810,12 +3806,14 @@
       <c r="A77" s="4">
         <v>73</v>
       </c>
-      <c r="B77" s="2"/>
+      <c r="B77" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="C77" s="4">
-        <v>157113</v>
+        <v>141657</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E77" s="4">
         <v>0</v>
@@ -3841,12 +3839,14 @@
       <c r="A78" s="4">
         <v>74</v>
       </c>
-      <c r="B78" s="2"/>
+      <c r="B78" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C78" s="4">
-        <v>157118</v>
+        <v>142753</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E78" s="4">
         <v>0</v>
@@ -3872,12 +3872,14 @@
       <c r="A79" s="4">
         <v>75</v>
       </c>
-      <c r="B79" s="2"/>
+      <c r="B79" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C79" s="4">
-        <v>157119</v>
+        <v>142751</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E79" s="4">
         <v>0</v>
@@ -3904,13 +3906,13 @@
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C80" s="4">
-        <v>271322</v>
+        <v>142951</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E80" s="4">
         <v>0</v>
@@ -3937,13 +3939,13 @@
         <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C81" s="4">
-        <v>311092</v>
+        <v>156399</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E81" s="4">
         <v>0</v>
@@ -3969,14 +3971,12 @@
       <c r="A82" s="4">
         <v>78</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="B82" s="2"/>
       <c r="C82" s="4">
-        <v>318586</v>
+        <v>157113</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E82" s="4">
         <v>0</v>
@@ -4004,10 +4004,10 @@
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="4">
-        <v>501294</v>
+        <v>157118</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E83" s="4">
         <v>0</v>
@@ -4033,14 +4033,12 @@
       <c r="A84" s="4">
         <v>80</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="4">
-        <v>127013</v>
+        <v>157119</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E84" s="4">
         <v>0</v>
@@ -4066,12 +4064,14 @@
       <c r="A85" s="4">
         <v>81</v>
       </c>
-      <c r="B85" s="2"/>
+      <c r="B85" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="C85" s="4">
-        <v>146328</v>
+        <v>271322</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E85" s="4">
         <v>0</v>
@@ -4097,12 +4097,14 @@
       <c r="A86" s="4">
         <v>82</v>
       </c>
-      <c r="B86" s="2"/>
+      <c r="B86" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="C86" s="4">
-        <v>146328</v>
+        <v>311092</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E86" s="4">
         <v>0</v>
@@ -4128,12 +4130,14 @@
       <c r="A87" s="4">
         <v>83</v>
       </c>
-      <c r="B87" s="2"/>
+      <c r="B87" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="C87" s="4">
-        <v>146753</v>
+        <v>318586</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E87" s="4">
         <v>0</v>
@@ -4159,14 +4163,12 @@
       <c r="A88" s="4">
         <v>84</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="B88" s="2"/>
       <c r="C88" s="4">
-        <v>146754</v>
+        <v>501294</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E88" s="4">
         <v>0</v>
@@ -4193,13 +4195,13 @@
         <v>85</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C89" s="4">
-        <v>144082</v>
+        <v>127013</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E89" s="4">
         <v>0</v>
@@ -4225,14 +4227,12 @@
       <c r="A90" s="4">
         <v>86</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="B90" s="2"/>
       <c r="C90" s="4">
-        <v>361275</v>
+        <v>146328</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E90" s="4">
         <v>0</v>
@@ -4255,11 +4255,19 @@
       <c r="U90" s="2"/>
     </row>
     <row r="91" spans="1:21">
-      <c r="A91" s="2"/>
+      <c r="A91" s="4">
+        <v>87</v>
+      </c>
       <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
+      <c r="C91" s="4">
+        <v>146328</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="4">
+        <v>0</v>
+      </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -4278,11 +4286,19 @@
       <c r="U91" s="2"/>
     </row>
     <row r="92" spans="1:21">
-      <c r="A92" s="2"/>
+      <c r="A92" s="4">
+        <v>88</v>
+      </c>
       <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
+      <c r="C92" s="4">
+        <v>146753</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="4">
+        <v>0</v>
+      </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -4301,11 +4317,21 @@
       <c r="U92" s="2"/>
     </row>
     <row r="93" spans="1:21">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
+      <c r="A93" s="4">
+        <v>89</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C93" s="4">
+        <v>146754</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="4">
+        <v>0</v>
+      </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -4324,11 +4350,21 @@
       <c r="U93" s="2"/>
     </row>
     <row r="94" spans="1:21">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
+      <c r="A94" s="4">
+        <v>90</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C94" s="4">
+        <v>144082</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="4">
+        <v>0</v>
+      </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -4347,11 +4383,21 @@
       <c r="U94" s="2"/>
     </row>
     <row r="95" spans="1:21">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
+      <c r="A95" s="4">
+        <v>91</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C95" s="4">
+        <v>361275</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="4">
+        <v>0</v>
+      </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -4370,11 +4416,19 @@
       <c r="U95" s="2"/>
     </row>
     <row r="96" spans="1:21">
-      <c r="A96" s="2"/>
+      <c r="A96" s="4">
+        <v>92</v>
+      </c>
       <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
+      <c r="C96" s="4">
+        <v>558271</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E96" s="4">
+        <v>0</v>
+      </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -7221,6 +7275,121 @@
       <c r="T219" s="2"/>
       <c r="U219" s="2"/>
     </row>
+    <row r="220" spans="1:21">
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+      <c r="J220" s="2"/>
+      <c r="K220" s="2"/>
+      <c r="L220" s="2"/>
+      <c r="M220" s="2"/>
+      <c r="N220" s="2"/>
+      <c r="O220" s="2"/>
+      <c r="P220" s="2"/>
+      <c r="Q220" s="2"/>
+      <c r="R220" s="2"/>
+      <c r="S220" s="2"/>
+      <c r="T220" s="2"/>
+      <c r="U220" s="2"/>
+    </row>
+    <row r="221" spans="1:21">
+      <c r="A221" s="2"/>
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
+      <c r="J221" s="2"/>
+      <c r="K221" s="2"/>
+      <c r="L221" s="2"/>
+      <c r="M221" s="2"/>
+      <c r="N221" s="2"/>
+      <c r="O221" s="2"/>
+      <c r="P221" s="2"/>
+      <c r="Q221" s="2"/>
+      <c r="R221" s="2"/>
+      <c r="S221" s="2"/>
+      <c r="T221" s="2"/>
+      <c r="U221" s="2"/>
+    </row>
+    <row r="222" spans="1:21">
+      <c r="A222" s="2"/>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
+      <c r="J222" s="2"/>
+      <c r="K222" s="2"/>
+      <c r="L222" s="2"/>
+      <c r="M222" s="2"/>
+      <c r="N222" s="2"/>
+      <c r="O222" s="2"/>
+      <c r="P222" s="2"/>
+      <c r="Q222" s="2"/>
+      <c r="R222" s="2"/>
+      <c r="S222" s="2"/>
+      <c r="T222" s="2"/>
+      <c r="U222" s="2"/>
+    </row>
+    <row r="223" spans="1:21">
+      <c r="A223" s="2"/>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+      <c r="J223" s="2"/>
+      <c r="K223" s="2"/>
+      <c r="L223" s="2"/>
+      <c r="M223" s="2"/>
+      <c r="N223" s="2"/>
+      <c r="O223" s="2"/>
+      <c r="P223" s="2"/>
+      <c r="Q223" s="2"/>
+      <c r="R223" s="2"/>
+      <c r="S223" s="2"/>
+      <c r="T223" s="2"/>
+      <c r="U223" s="2"/>
+    </row>
+    <row r="224" spans="1:21">
+      <c r="A224" s="2"/>
+      <c r="B224" s="2"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
+      <c r="E224" s="2"/>
+      <c r="F224" s="2"/>
+      <c r="G224" s="2"/>
+      <c r="H224" s="2"/>
+      <c r="I224" s="2"/>
+      <c r="J224" s="2"/>
+      <c r="K224" s="2"/>
+      <c r="L224" s="2"/>
+      <c r="M224" s="2"/>
+      <c r="N224" s="2"/>
+      <c r="O224" s="2"/>
+      <c r="P224" s="2"/>
+      <c r="Q224" s="2"/>
+      <c r="R224" s="2"/>
+      <c r="S224" s="2"/>
+      <c r="T224" s="2"/>
+      <c r="U224" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/rp/Excel/Effects_特效.xlsx
+++ b/rp/Excel/Effects_特效.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="500"/>
+    <workbookView windowWidth="24750" windowHeight="12060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="51">
   <si>
     <t>Int</t>
   </si>
@@ -58,7 +58,13 @@
 2-FeMale</t>
   </si>
   <si>
+    <t>0|0|100|0|0|0|0.1|0.1|0.1</t>
+  </si>
+  <si>
     <t>0|0|0|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|100|0|0|0|0.1|0.02|0.1</t>
   </si>
   <si>
     <t>广告牌</t>
@@ -1366,7 +1372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U219"/>
+  <dimension ref="A1:U224"/>
   <sheetFormatPr defaultColWidth="12.0666666666667" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="12.0666666666667" style="1"/>
@@ -1494,7 +1500,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="4">
-        <v>556585</v>
+        <v>681318</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -1525,10 +1531,10 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>674918</v>
+        <v>687895</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
@@ -1556,10 +1562,10 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="4">
-        <v>565350</v>
+        <v>687897</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" s="4">
         <v>0</v>
@@ -1587,10 +1593,10 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="4">
-        <v>567138</v>
+        <v>687899</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
@@ -1618,10 +1624,10 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="4">
-        <v>567139</v>
+        <v>688276</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
@@ -1649,10 +1655,10 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="4">
-        <v>525387</v>
+        <v>556585</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4">
         <v>0</v>
@@ -1680,10 +1686,10 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="4">
-        <v>501310</v>
+        <v>674918</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4">
         <v>0</v>
@@ -1709,14 +1715,12 @@
       <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="4">
+        <v>565350</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C12" s="4">
-        <v>57202</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -1742,14 +1746,12 @@
       <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B13" s="2"/>
       <c r="C13" s="4">
-        <v>365194</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>13</v>
+        <v>567138</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
@@ -1775,14 +1777,12 @@
       <c r="A14" s="4">
         <v>10</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B14" s="2"/>
       <c r="C14" s="4">
-        <v>28451</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>15</v>
+        <v>567139</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -1808,14 +1808,12 @@
       <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>16</v>
-      </c>
+      <c r="B15" s="2"/>
       <c r="C15" s="4">
-        <v>526080</v>
+        <v>525387</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -1841,12 +1839,12 @@
       <c r="A16" s="4">
         <v>12</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="2"/>
       <c r="C16" s="4">
-        <v>464265</v>
+        <v>501310</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1872,12 +1870,14 @@
       <c r="A17" s="4">
         <v>13</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C17" s="4">
-        <v>266517</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>17</v>
+        <v>57202</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
@@ -1903,12 +1903,14 @@
       <c r="A18" s="4">
         <v>14</v>
       </c>
-      <c r="B18" s="6"/>
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="C18" s="4">
-        <v>266518</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>17</v>
+        <v>365194</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -1934,11 +1936,13 @@
       <c r="A19" s="4">
         <v>15</v>
       </c>
-      <c r="B19" s="6"/>
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C19" s="4">
-        <v>266519</v>
-      </c>
-      <c r="D19" s="2" t="s">
+        <v>28451</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E19" s="4">
@@ -1965,12 +1969,14 @@
       <c r="A20" s="4">
         <v>16</v>
       </c>
-      <c r="B20" s="6"/>
+      <c r="B20" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="C20" s="4">
-        <v>266520</v>
+        <v>526080</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E20" s="4">
         <v>0</v>
@@ -1998,10 +2004,10 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="4">
-        <v>266521</v>
+        <v>464265</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E21" s="4">
         <v>0</v>
@@ -2029,10 +2035,10 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="4">
-        <v>439411</v>
+        <v>266517</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
@@ -2060,10 +2066,10 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="4">
-        <v>484531</v>
+        <v>266518</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -2091,10 +2097,10 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="4">
-        <v>144088</v>
+        <v>266519</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -2122,7 +2128,7 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="4">
-        <v>439415</v>
+        <v>266520</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>19</v>
@@ -2153,10 +2159,10 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="4">
-        <v>144093</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>20</v>
+        <v>266521</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -2184,10 +2190,10 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="4">
-        <v>326212</v>
+        <v>439411</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27" s="4">
         <v>0</v>
@@ -2215,10 +2221,10 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="4">
-        <v>326224</v>
+        <v>484531</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -2246,10 +2252,10 @@
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="4">
-        <v>383667</v>
+        <v>144088</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -2277,7 +2283,7 @@
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="4">
-        <v>383676</v>
+        <v>439415</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>21</v>
@@ -2308,10 +2314,10 @@
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="4">
-        <v>386040</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>21</v>
+        <v>144093</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="E31" s="4">
         <v>0</v>
@@ -2339,10 +2345,10 @@
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="4">
-        <v>394667</v>
+        <v>326212</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
@@ -2370,10 +2376,10 @@
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="4">
-        <v>394678</v>
+        <v>326224</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E33" s="4">
         <v>0</v>
@@ -2399,13 +2405,11 @@
       <c r="A34" s="4">
         <v>30</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="B34" s="6"/>
       <c r="C34" s="4">
-        <v>220840</v>
-      </c>
-      <c r="D34" s="5" t="s">
+        <v>383667</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E34" s="4">
@@ -2428,16 +2432,16 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
     </row>
-    <row r="35" ht="17.25" spans="1:21">
+    <row r="35" spans="1:21">
       <c r="A35" s="4">
         <v>31</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="7">
-        <v>485354</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>24</v>
+      <c r="B35" s="6"/>
+      <c r="C35" s="4">
+        <v>383676</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -2463,13 +2467,11 @@
       <c r="A36" s="4">
         <v>32</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B36" s="6"/>
       <c r="C36" s="4">
-        <v>220841</v>
-      </c>
-      <c r="D36" s="5" t="s">
+        <v>386040</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E36" s="4">
@@ -2496,13 +2498,11 @@
       <c r="A37" s="4">
         <v>33</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B37" s="6"/>
       <c r="C37" s="4">
-        <v>220842</v>
-      </c>
-      <c r="D37" s="5" t="s">
+        <v>394667</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E37" s="4">
@@ -2529,13 +2529,11 @@
       <c r="A38" s="4">
         <v>34</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="B38" s="6"/>
       <c r="C38" s="4">
-        <v>220843</v>
-      </c>
-      <c r="D38" s="5" t="s">
+        <v>394678</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E38" s="4">
@@ -2562,14 +2560,14 @@
       <c r="A39" s="4">
         <v>35</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>22</v>
+      <c r="B39" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C39" s="4">
-        <v>220844</v>
+        <v>220840</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -2591,18 +2589,16 @@
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" ht="17.25" spans="1:21">
       <c r="A40" s="4">
         <v>36</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" s="4">
-        <v>220845</v>
+      <c r="B40" s="2"/>
+      <c r="C40" s="7">
+        <v>485354</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
@@ -2628,14 +2624,14 @@
       <c r="A41" s="4">
         <v>37</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>22</v>
+      <c r="B41" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C41" s="4">
-        <v>220846</v>
+        <v>220841</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
@@ -2662,13 +2658,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C42" s="4">
-        <v>220847</v>
+        <v>220842</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
@@ -2694,14 +2690,14 @@
       <c r="A43" s="4">
         <v>39</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>22</v>
+      <c r="B43" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C43" s="4">
-        <v>220848</v>
+        <v>220843</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
@@ -2727,14 +2723,14 @@
       <c r="A44" s="4">
         <v>40</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>22</v>
+      <c r="B44" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C44" s="4">
-        <v>220849</v>
+        <v>220844</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
@@ -2761,13 +2757,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C45" s="4">
-        <v>220850</v>
+        <v>220845</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -2793,14 +2789,14 @@
       <c r="A46" s="4">
         <v>42</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>22</v>
+      <c r="B46" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C46" s="4">
-        <v>220851</v>
+        <v>220846</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
@@ -2826,14 +2822,14 @@
       <c r="A47" s="4">
         <v>43</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>22</v>
+      <c r="B47" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C47" s="4">
-        <v>220041</v>
+        <v>220847</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E47" s="4">
         <v>0</v>
@@ -2860,13 +2856,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C48" s="4">
-        <v>220469</v>
+        <v>220848</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E48" s="4">
         <v>0</v>
@@ -2892,14 +2888,14 @@
       <c r="A49" s="4">
         <v>45</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="4">
+        <v>220849</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="C49" s="4">
-        <v>31645</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -2926,13 +2922,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C50" s="4">
-        <v>4366</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>9</v>
+        <v>220850</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -2959,13 +2955,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C51" s="4">
-        <v>4367</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>9</v>
+        <v>220851</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -2991,14 +2987,14 @@
       <c r="A52" s="4">
         <v>48</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>28</v>
+      <c r="B52" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C52" s="4">
-        <v>4368</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>9</v>
+        <v>220041</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -3024,12 +3020,14 @@
       <c r="A53" s="4">
         <v>49</v>
       </c>
-      <c r="B53" s="2"/>
+      <c r="B53" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C53" s="4">
-        <v>144084</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>29</v>
+        <v>220469</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E53" s="4">
         <v>0</v>
@@ -3055,12 +3053,14 @@
       <c r="A54" s="4">
         <v>50</v>
       </c>
-      <c r="B54" s="2"/>
+      <c r="B54" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C54" s="4">
-        <v>146786</v>
+        <v>31645</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E54" s="4">
         <v>0</v>
@@ -3086,12 +3086,14 @@
       <c r="A55" s="4">
         <v>51</v>
       </c>
-      <c r="B55" s="2"/>
+      <c r="B55" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C55" s="4">
-        <v>144083</v>
+        <v>4366</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E55" s="4">
         <v>0</v>
@@ -3118,13 +3120,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C56" s="4">
-        <v>32240</v>
+        <v>4367</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E56" s="4">
         <v>0</v>
@@ -3154,10 +3156,10 @@
         <v>30</v>
       </c>
       <c r="C57" s="4">
-        <v>59956</v>
+        <v>4368</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
@@ -3183,14 +3185,12 @@
       <c r="A58" s="4">
         <v>54</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="2"/>
+      <c r="C58" s="4">
+        <v>144084</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C58" s="4">
-        <v>73402</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E58" s="4">
         <v>0</v>
@@ -3216,14 +3216,12 @@
       <c r="A59" s="4">
         <v>55</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="B59" s="2"/>
       <c r="C59" s="4">
-        <v>88762</v>
+        <v>146786</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E59" s="4">
         <v>0</v>
@@ -3249,14 +3247,12 @@
       <c r="A60" s="4">
         <v>56</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="B60" s="2"/>
       <c r="C60" s="4">
-        <v>88773</v>
+        <v>144083</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E60" s="4">
         <v>0</v>
@@ -3283,13 +3279,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C61" s="4">
-        <v>89073</v>
+        <v>32240</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E61" s="4">
         <v>0</v>
@@ -3316,13 +3312,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C62" s="4">
-        <v>89109</v>
+        <v>59956</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E62" s="4">
         <v>0</v>
@@ -3349,13 +3345,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C63" s="4">
-        <v>89111</v>
+        <v>73402</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E63" s="4">
         <v>0</v>
@@ -3385,10 +3381,10 @@
         <v>34</v>
       </c>
       <c r="C64" s="4">
-        <v>89112</v>
+        <v>88762</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E64" s="4">
         <v>0</v>
@@ -3415,13 +3411,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C65" s="4">
-        <v>89122</v>
+        <v>88773</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E65" s="4">
         <v>0</v>
@@ -3448,13 +3444,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C66" s="4">
-        <v>113903</v>
+        <v>89073</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E66" s="4">
         <v>0</v>
@@ -3481,13 +3477,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C67" s="4">
-        <v>113913</v>
+        <v>89109</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E67" s="4">
         <v>0</v>
@@ -3514,13 +3510,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C68" s="4">
-        <v>113907</v>
+        <v>89111</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E68" s="4">
         <v>0</v>
@@ -3547,13 +3543,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C69" s="4">
-        <v>119917</v>
+        <v>89112</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E69" s="4">
         <v>0</v>
@@ -3580,13 +3576,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C70" s="4">
-        <v>130776</v>
+        <v>89122</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E70" s="4">
         <v>0</v>
@@ -3613,13 +3609,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C71" s="4">
-        <v>141655</v>
+        <v>113903</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E71" s="4">
         <v>0</v>
@@ -3646,13 +3642,13 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C72" s="4">
-        <v>141657</v>
+        <v>113913</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E72" s="4">
         <v>0</v>
@@ -3679,13 +3675,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C73" s="4">
-        <v>142753</v>
+        <v>113907</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E73" s="4">
         <v>0</v>
@@ -3715,10 +3711,10 @@
         <v>40</v>
       </c>
       <c r="C74" s="4">
-        <v>142751</v>
+        <v>119917</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E74" s="4">
         <v>0</v>
@@ -3745,13 +3741,13 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C75" s="4">
-        <v>142951</v>
+        <v>130776</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75" s="4">
         <v>0</v>
@@ -3781,10 +3777,10 @@
         <v>41</v>
       </c>
       <c r="C76" s="4">
-        <v>156399</v>
+        <v>141655</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" s="4">
         <v>0</v>
@@ -3810,12 +3806,14 @@
       <c r="A77" s="4">
         <v>73</v>
       </c>
-      <c r="B77" s="2"/>
+      <c r="B77" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="C77" s="4">
-        <v>157113</v>
+        <v>141657</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E77" s="4">
         <v>0</v>
@@ -3841,12 +3839,14 @@
       <c r="A78" s="4">
         <v>74</v>
       </c>
-      <c r="B78" s="2"/>
+      <c r="B78" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C78" s="4">
-        <v>157118</v>
+        <v>142753</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E78" s="4">
         <v>0</v>
@@ -3872,12 +3872,14 @@
       <c r="A79" s="4">
         <v>75</v>
       </c>
-      <c r="B79" s="2"/>
+      <c r="B79" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C79" s="4">
-        <v>157119</v>
+        <v>142751</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E79" s="4">
         <v>0</v>
@@ -3904,13 +3906,13 @@
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C80" s="4">
-        <v>271322</v>
+        <v>142951</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E80" s="4">
         <v>0</v>
@@ -3940,10 +3942,10 @@
         <v>43</v>
       </c>
       <c r="C81" s="4">
-        <v>311092</v>
+        <v>156399</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E81" s="4">
         <v>0</v>
@@ -3969,14 +3971,12 @@
       <c r="A82" s="4">
         <v>78</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="B82" s="2"/>
       <c r="C82" s="4">
-        <v>318586</v>
+        <v>157113</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E82" s="4">
         <v>0</v>
@@ -4004,10 +4004,10 @@
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="4">
-        <v>501294</v>
+        <v>157118</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E83" s="4">
         <v>0</v>
@@ -4033,14 +4033,12 @@
       <c r="A84" s="4">
         <v>80</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="4">
-        <v>127013</v>
+        <v>157119</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E84" s="4">
         <v>0</v>
@@ -4066,12 +4064,14 @@
       <c r="A85" s="4">
         <v>81</v>
       </c>
-      <c r="B85" s="2"/>
+      <c r="B85" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="C85" s="4">
-        <v>146328</v>
+        <v>271322</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E85" s="4">
         <v>0</v>
@@ -4097,12 +4097,14 @@
       <c r="A86" s="4">
         <v>82</v>
       </c>
-      <c r="B86" s="2"/>
+      <c r="B86" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="C86" s="4">
-        <v>146328</v>
+        <v>311092</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E86" s="4">
         <v>0</v>
@@ -4128,12 +4130,14 @@
       <c r="A87" s="4">
         <v>83</v>
       </c>
-      <c r="B87" s="2"/>
+      <c r="B87" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="C87" s="4">
-        <v>146753</v>
+        <v>318586</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E87" s="4">
         <v>0</v>
@@ -4159,14 +4163,12 @@
       <c r="A88" s="4">
         <v>84</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="B88" s="2"/>
       <c r="C88" s="4">
-        <v>146754</v>
+        <v>501294</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E88" s="4">
         <v>0</v>
@@ -4193,13 +4195,13 @@
         <v>85</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="C89" s="4">
-        <v>144082</v>
+        <v>127013</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E89" s="4">
         <v>0</v>
@@ -4225,14 +4227,12 @@
       <c r="A90" s="4">
         <v>86</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="B90" s="2"/>
       <c r="C90" s="4">
-        <v>361275</v>
+        <v>146328</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E90" s="4">
         <v>0</v>
@@ -4260,10 +4260,10 @@
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="4">
-        <v>558271</v>
+        <v>146328</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E91" s="4">
         <v>0</v>
@@ -4286,11 +4286,19 @@
       <c r="U91" s="2"/>
     </row>
     <row r="92" spans="1:21">
-      <c r="A92" s="2"/>
+      <c r="A92" s="4">
+        <v>88</v>
+      </c>
       <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
+      <c r="C92" s="4">
+        <v>146753</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="4">
+        <v>0</v>
+      </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -4309,11 +4317,21 @@
       <c r="U92" s="2"/>
     </row>
     <row r="93" spans="1:21">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
+      <c r="A93" s="4">
+        <v>89</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C93" s="4">
+        <v>146754</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="4">
+        <v>0</v>
+      </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -4332,11 +4350,21 @@
       <c r="U93" s="2"/>
     </row>
     <row r="94" spans="1:21">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
+      <c r="A94" s="4">
+        <v>90</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C94" s="4">
+        <v>144082</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="4">
+        <v>0</v>
+      </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -4355,11 +4383,21 @@
       <c r="U94" s="2"/>
     </row>
     <row r="95" spans="1:21">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
+      <c r="A95" s="4">
+        <v>91</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C95" s="4">
+        <v>361275</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="4">
+        <v>0</v>
+      </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -4378,11 +4416,19 @@
       <c r="U95" s="2"/>
     </row>
     <row r="96" spans="1:21">
-      <c r="A96" s="2"/>
+      <c r="A96" s="4">
+        <v>92</v>
+      </c>
       <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
+      <c r="C96" s="4">
+        <v>558271</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E96" s="4">
+        <v>0</v>
+      </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -7229,6 +7275,121 @@
       <c r="T219" s="2"/>
       <c r="U219" s="2"/>
     </row>
+    <row r="220" spans="1:21">
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+      <c r="J220" s="2"/>
+      <c r="K220" s="2"/>
+      <c r="L220" s="2"/>
+      <c r="M220" s="2"/>
+      <c r="N220" s="2"/>
+      <c r="O220" s="2"/>
+      <c r="P220" s="2"/>
+      <c r="Q220" s="2"/>
+      <c r="R220" s="2"/>
+      <c r="S220" s="2"/>
+      <c r="T220" s="2"/>
+      <c r="U220" s="2"/>
+    </row>
+    <row r="221" spans="1:21">
+      <c r="A221" s="2"/>
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
+      <c r="J221" s="2"/>
+      <c r="K221" s="2"/>
+      <c r="L221" s="2"/>
+      <c r="M221" s="2"/>
+      <c r="N221" s="2"/>
+      <c r="O221" s="2"/>
+      <c r="P221" s="2"/>
+      <c r="Q221" s="2"/>
+      <c r="R221" s="2"/>
+      <c r="S221" s="2"/>
+      <c r="T221" s="2"/>
+      <c r="U221" s="2"/>
+    </row>
+    <row r="222" spans="1:21">
+      <c r="A222" s="2"/>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
+      <c r="J222" s="2"/>
+      <c r="K222" s="2"/>
+      <c r="L222" s="2"/>
+      <c r="M222" s="2"/>
+      <c r="N222" s="2"/>
+      <c r="O222" s="2"/>
+      <c r="P222" s="2"/>
+      <c r="Q222" s="2"/>
+      <c r="R222" s="2"/>
+      <c r="S222" s="2"/>
+      <c r="T222" s="2"/>
+      <c r="U222" s="2"/>
+    </row>
+    <row r="223" spans="1:21">
+      <c r="A223" s="2"/>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+      <c r="J223" s="2"/>
+      <c r="K223" s="2"/>
+      <c r="L223" s="2"/>
+      <c r="M223" s="2"/>
+      <c r="N223" s="2"/>
+      <c r="O223" s="2"/>
+      <c r="P223" s="2"/>
+      <c r="Q223" s="2"/>
+      <c r="R223" s="2"/>
+      <c r="S223" s="2"/>
+      <c r="T223" s="2"/>
+      <c r="U223" s="2"/>
+    </row>
+    <row r="224" spans="1:21">
+      <c r="A224" s="2"/>
+      <c r="B224" s="2"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
+      <c r="E224" s="2"/>
+      <c r="F224" s="2"/>
+      <c r="G224" s="2"/>
+      <c r="H224" s="2"/>
+      <c r="I224" s="2"/>
+      <c r="J224" s="2"/>
+      <c r="K224" s="2"/>
+      <c r="L224" s="2"/>
+      <c r="M224" s="2"/>
+      <c r="N224" s="2"/>
+      <c r="O224" s="2"/>
+      <c r="P224" s="2"/>
+      <c r="Q224" s="2"/>
+      <c r="R224" s="2"/>
+      <c r="S224" s="2"/>
+      <c r="T224" s="2"/>
+      <c r="U224" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/rp/Excel/Effects_特效.xlsx
+++ b/rp/Excel/Effects_特效.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="500"/>
+    <workbookView windowWidth="24750" windowHeight="12060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="51">
   <si>
     <t>Int</t>
   </si>
@@ -58,7 +58,13 @@
 2-FeMale</t>
   </si>
   <si>
+    <t>0|0|100|0|0|0|0.1|0.1|0.1</t>
+  </si>
+  <si>
     <t>0|0|0|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|100|0|0|0|0.1|0.02|0.1</t>
   </si>
   <si>
     <t>广告牌</t>
@@ -173,6 +179,9 @@
   </si>
   <si>
     <t>剪纸</t>
+  </si>
+  <si>
+    <t>0|0|150|0|0|0|1|1|1</t>
   </si>
 </sst>
 </file>
@@ -1363,7 +1372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U214"/>
+  <dimension ref="A1:U224"/>
   <sheetFormatPr defaultColWidth="12.0666666666667" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="12.0666666666667" style="1"/>
@@ -1491,7 +1500,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="4">
-        <v>525387</v>
+        <v>681318</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -1522,10 +1531,10 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>501310</v>
+        <v>687895</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
@@ -1551,14 +1560,12 @@
       <c r="A7" s="4">
         <v>3</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="4">
+        <v>687897</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C7" s="4">
-        <v>57202</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="E7" s="4">
         <v>0</v>
@@ -1584,14 +1591,12 @@
       <c r="A8" s="4">
         <v>4</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="4">
-        <v>365194</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>13</v>
+        <v>687899</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
@@ -1617,14 +1622,12 @@
       <c r="A9" s="4">
         <v>5</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="4">
-        <v>28451</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>15</v>
+        <v>688276</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
@@ -1650,14 +1653,12 @@
       <c r="A10" s="4">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>16</v>
-      </c>
+      <c r="B10" s="2"/>
       <c r="C10" s="4">
-        <v>526080</v>
+        <v>556585</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4">
         <v>0</v>
@@ -1683,12 +1684,12 @@
       <c r="A11" s="4">
         <v>7</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="2"/>
       <c r="C11" s="4">
-        <v>464265</v>
+        <v>674918</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4">
         <v>0</v>
@@ -1714,12 +1715,12 @@
       <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="6"/>
+      <c r="B12" s="2"/>
       <c r="C12" s="4">
-        <v>266517</v>
+        <v>565350</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -1745,12 +1746,12 @@
       <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
+      <c r="B13" s="2"/>
       <c r="C13" s="4">
-        <v>266518</v>
+        <v>567138</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
@@ -1776,12 +1777,12 @@
       <c r="A14" s="4">
         <v>10</v>
       </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="2"/>
       <c r="C14" s="4">
-        <v>266519</v>
+        <v>567139</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -1807,12 +1808,12 @@
       <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="6"/>
+      <c r="B15" s="2"/>
       <c r="C15" s="4">
-        <v>266520</v>
+        <v>525387</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -1838,12 +1839,12 @@
       <c r="A16" s="4">
         <v>12</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="2"/>
       <c r="C16" s="4">
-        <v>266521</v>
+        <v>501310</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1869,12 +1870,14 @@
       <c r="A17" s="4">
         <v>13</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C17" s="4">
-        <v>439411</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>18</v>
+        <v>57202</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
@@ -1900,12 +1903,14 @@
       <c r="A18" s="4">
         <v>14</v>
       </c>
-      <c r="B18" s="6"/>
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="C18" s="4">
-        <v>484531</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>365194</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -1931,12 +1936,14 @@
       <c r="A19" s="4">
         <v>15</v>
       </c>
-      <c r="B19" s="6"/>
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C19" s="4">
-        <v>144088</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>28451</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -1962,12 +1969,14 @@
       <c r="A20" s="4">
         <v>16</v>
       </c>
-      <c r="B20" s="6"/>
+      <c r="B20" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="C20" s="4">
-        <v>439415</v>
+        <v>526080</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E20" s="4">
         <v>0</v>
@@ -1995,10 +2004,10 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="4">
-        <v>144093</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>20</v>
+        <v>464265</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E21" s="4">
         <v>0</v>
@@ -2026,10 +2035,10 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="4">
-        <v>326212</v>
+        <v>266517</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
@@ -2057,10 +2066,10 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="4">
-        <v>326224</v>
+        <v>266518</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -2088,10 +2097,10 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="4">
-        <v>383667</v>
+        <v>266519</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -2119,10 +2128,10 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="4">
-        <v>383676</v>
+        <v>266520</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -2150,10 +2159,10 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="4">
-        <v>386040</v>
+        <v>266521</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -2181,10 +2190,10 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="4">
-        <v>394667</v>
+        <v>439411</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27" s="4">
         <v>0</v>
@@ -2212,10 +2221,10 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="4">
-        <v>394678</v>
+        <v>484531</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -2241,14 +2250,12 @@
       <c r="A29" s="4">
         <v>25</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="B29" s="6"/>
       <c r="C29" s="4">
-        <v>220840</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>23</v>
+        <v>144088</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -2270,16 +2277,16 @@
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
     </row>
-    <row r="30" ht="17.25" spans="1:21">
+    <row r="30" spans="1:21">
       <c r="A30" s="4">
         <v>26</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="7">
-        <v>485354</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>24</v>
+      <c r="B30" s="6"/>
+      <c r="C30" s="4">
+        <v>439415</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
@@ -2305,14 +2312,12 @@
       <c r="A31" s="4">
         <v>27</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="6"/>
+      <c r="C31" s="4">
+        <v>144093</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="C31" s="4">
-        <v>220841</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="E31" s="4">
         <v>0</v>
@@ -2338,13 +2343,11 @@
       <c r="A32" s="4">
         <v>28</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B32" s="6"/>
       <c r="C32" s="4">
-        <v>220842</v>
-      </c>
-      <c r="D32" s="5" t="s">
+        <v>326212</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E32" s="4">
@@ -2371,13 +2374,11 @@
       <c r="A33" s="4">
         <v>29</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="B33" s="6"/>
       <c r="C33" s="4">
-        <v>220843</v>
-      </c>
-      <c r="D33" s="5" t="s">
+        <v>326224</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E33" s="4">
@@ -2404,13 +2405,11 @@
       <c r="A34" s="4">
         <v>30</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B34" s="6"/>
       <c r="C34" s="4">
-        <v>220844</v>
-      </c>
-      <c r="D34" s="5" t="s">
+        <v>383667</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E34" s="4">
@@ -2437,13 +2436,11 @@
       <c r="A35" s="4">
         <v>31</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B35" s="6"/>
       <c r="C35" s="4">
-        <v>220845</v>
-      </c>
-      <c r="D35" s="5" t="s">
+        <v>383676</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E35" s="4">
@@ -2470,13 +2467,11 @@
       <c r="A36" s="4">
         <v>32</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="B36" s="6"/>
       <c r="C36" s="4">
-        <v>220846</v>
-      </c>
-      <c r="D36" s="5" t="s">
+        <v>386040</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E36" s="4">
@@ -2503,13 +2498,11 @@
       <c r="A37" s="4">
         <v>33</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B37" s="6"/>
       <c r="C37" s="4">
-        <v>220847</v>
-      </c>
-      <c r="D37" s="5" t="s">
+        <v>394667</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E37" s="4">
@@ -2536,13 +2529,11 @@
       <c r="A38" s="4">
         <v>34</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B38" s="6"/>
       <c r="C38" s="4">
-        <v>220848</v>
-      </c>
-      <c r="D38" s="5" t="s">
+        <v>394678</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E38" s="4">
@@ -2570,13 +2561,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C39" s="4">
-        <v>220849</v>
+        <v>220840</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -2598,18 +2589,16 @@
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" ht="17.25" spans="1:21">
       <c r="A40" s="4">
         <v>36</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" s="4">
-        <v>220850</v>
+      <c r="B40" s="2"/>
+      <c r="C40" s="7">
+        <v>485354</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
@@ -2636,13 +2625,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C41" s="4">
-        <v>220851</v>
+        <v>220841</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
@@ -2668,14 +2657,14 @@
       <c r="A42" s="4">
         <v>38</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>22</v>
+      <c r="B42" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C42" s="4">
-        <v>220041</v>
+        <v>220842</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
@@ -2701,14 +2690,14 @@
       <c r="A43" s="4">
         <v>39</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>22</v>
+      <c r="B43" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C43" s="4">
-        <v>220469</v>
+        <v>220843</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
@@ -2735,13 +2724,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="4">
+        <v>220844</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="C44" s="4">
-        <v>31645</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
@@ -2768,13 +2757,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C45" s="4">
-        <v>4366</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>9</v>
+        <v>220845</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -2800,14 +2789,14 @@
       <c r="A46" s="4">
         <v>42</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>27</v>
+      <c r="B46" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C46" s="4">
-        <v>4367</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>9</v>
+        <v>220846</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
@@ -2834,13 +2823,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C47" s="4">
-        <v>4368</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>9</v>
+        <v>220847</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E47" s="4">
         <v>0</v>
@@ -2866,12 +2855,14 @@
       <c r="A48" s="4">
         <v>44</v>
       </c>
-      <c r="B48" s="2"/>
+      <c r="B48" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C48" s="4">
-        <v>144084</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>29</v>
+        <v>220848</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E48" s="4">
         <v>0</v>
@@ -2897,12 +2888,14 @@
       <c r="A49" s="4">
         <v>45</v>
       </c>
-      <c r="B49" s="2"/>
+      <c r="B49" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="C49" s="4">
-        <v>146786</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>9</v>
+        <v>220849</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -2928,12 +2921,14 @@
       <c r="A50" s="4">
         <v>46</v>
       </c>
-      <c r="B50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C50" s="4">
-        <v>144083</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>29</v>
+        <v>220850</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -2960,13 +2955,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C51" s="4">
-        <v>32240</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>9</v>
+        <v>220851</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -2992,14 +2987,14 @@
       <c r="A52" s="4">
         <v>48</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>30</v>
+      <c r="B52" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C52" s="4">
-        <v>59956</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>9</v>
+        <v>220041</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -3026,13 +3021,13 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C53" s="4">
-        <v>73402</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>9</v>
+        <v>220469</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E53" s="4">
         <v>0</v>
@@ -3059,13 +3054,13 @@
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C54" s="4">
-        <v>88762</v>
+        <v>31645</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E54" s="4">
         <v>0</v>
@@ -3092,13 +3087,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C55" s="4">
-        <v>88773</v>
+        <v>4366</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E55" s="4">
         <v>0</v>
@@ -3125,13 +3120,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C56" s="4">
-        <v>89073</v>
+        <v>4367</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E56" s="4">
         <v>0</v>
@@ -3158,13 +3153,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C57" s="4">
-        <v>89109</v>
+        <v>4368</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
@@ -3190,14 +3185,12 @@
       <c r="A58" s="4">
         <v>54</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="B58" s="2"/>
       <c r="C58" s="4">
-        <v>89111</v>
+        <v>144084</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E58" s="4">
         <v>0</v>
@@ -3223,14 +3216,12 @@
       <c r="A59" s="4">
         <v>55</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="B59" s="2"/>
       <c r="C59" s="4">
-        <v>89112</v>
+        <v>146786</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E59" s="4">
         <v>0</v>
@@ -3256,14 +3247,12 @@
       <c r="A60" s="4">
         <v>56</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="B60" s="2"/>
       <c r="C60" s="4">
-        <v>89122</v>
+        <v>144083</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E60" s="4">
         <v>0</v>
@@ -3290,13 +3279,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C61" s="4">
-        <v>113903</v>
+        <v>32240</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E61" s="4">
         <v>0</v>
@@ -3323,13 +3312,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C62" s="4">
-        <v>113913</v>
+        <v>59956</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E62" s="4">
         <v>0</v>
@@ -3356,13 +3345,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C63" s="4">
-        <v>113907</v>
+        <v>73402</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E63" s="4">
         <v>0</v>
@@ -3389,13 +3378,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C64" s="4">
-        <v>119917</v>
+        <v>88762</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E64" s="4">
         <v>0</v>
@@ -3422,13 +3411,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C65" s="4">
-        <v>130776</v>
+        <v>88773</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E65" s="4">
         <v>0</v>
@@ -3455,13 +3444,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C66" s="4">
-        <v>141655</v>
+        <v>89073</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E66" s="4">
         <v>0</v>
@@ -3488,13 +3477,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C67" s="4">
-        <v>141657</v>
+        <v>89109</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E67" s="4">
         <v>0</v>
@@ -3521,13 +3510,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C68" s="4">
-        <v>142753</v>
+        <v>89111</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E68" s="4">
         <v>0</v>
@@ -3554,13 +3543,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C69" s="4">
-        <v>142751</v>
+        <v>89112</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E69" s="4">
         <v>0</v>
@@ -3587,13 +3576,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C70" s="4">
-        <v>142951</v>
+        <v>89122</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E70" s="4">
         <v>0</v>
@@ -3620,13 +3609,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C71" s="4">
-        <v>156399</v>
+        <v>113903</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E71" s="4">
         <v>0</v>
@@ -3652,12 +3641,14 @@
       <c r="A72" s="4">
         <v>68</v>
       </c>
-      <c r="B72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C72" s="4">
-        <v>157113</v>
+        <v>113913</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E72" s="4">
         <v>0</v>
@@ -3683,12 +3674,14 @@
       <c r="A73" s="4">
         <v>69</v>
       </c>
-      <c r="B73" s="2"/>
+      <c r="B73" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="C73" s="4">
-        <v>157118</v>
+        <v>113907</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E73" s="4">
         <v>0</v>
@@ -3714,12 +3707,14 @@
       <c r="A74" s="4">
         <v>70</v>
       </c>
-      <c r="B74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="C74" s="4">
-        <v>157119</v>
+        <v>119917</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E74" s="4">
         <v>0</v>
@@ -3746,13 +3741,13 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C75" s="4">
-        <v>271322</v>
+        <v>130776</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75" s="4">
         <v>0</v>
@@ -3779,13 +3774,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C76" s="4">
-        <v>311092</v>
+        <v>141655</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" s="4">
         <v>0</v>
@@ -3812,13 +3807,13 @@
         <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C77" s="4">
-        <v>318586</v>
+        <v>141657</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E77" s="4">
         <v>0</v>
@@ -3844,12 +3839,14 @@
       <c r="A78" s="4">
         <v>74</v>
       </c>
-      <c r="B78" s="2"/>
+      <c r="B78" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C78" s="4">
-        <v>501294</v>
+        <v>142753</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E78" s="4">
         <v>0</v>
@@ -3876,13 +3873,13 @@
         <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C79" s="4">
-        <v>127013</v>
+        <v>142751</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E79" s="4">
         <v>0</v>
@@ -3908,12 +3905,14 @@
       <c r="A80" s="4">
         <v>76</v>
       </c>
-      <c r="B80" s="2"/>
+      <c r="B80" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C80" s="4">
-        <v>146328</v>
+        <v>142951</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E80" s="4">
         <v>0</v>
@@ -3939,12 +3938,14 @@
       <c r="A81" s="4">
         <v>77</v>
       </c>
-      <c r="B81" s="2"/>
+      <c r="B81" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="C81" s="4">
-        <v>146328</v>
+        <v>156399</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E81" s="4">
         <v>0</v>
@@ -3972,10 +3973,10 @@
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="4">
-        <v>146753</v>
+        <v>157113</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E82" s="4">
         <v>0</v>
@@ -4001,14 +4002,12 @@
       <c r="A83" s="4">
         <v>79</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="B83" s="2"/>
       <c r="C83" s="4">
-        <v>146754</v>
+        <v>157118</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E83" s="4">
         <v>0</v>
@@ -4034,14 +4033,12 @@
       <c r="A84" s="4">
         <v>80</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="4">
-        <v>144082</v>
+        <v>157119</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E84" s="4">
         <v>0</v>
@@ -4068,13 +4065,13 @@
         <v>81</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C85" s="4">
-        <v>361275</v>
+        <v>271322</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E85" s="4">
         <v>0</v>
@@ -4097,11 +4094,21 @@
       <c r="U85" s="2"/>
     </row>
     <row r="86" spans="1:21">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
+      <c r="A86" s="4">
+        <v>82</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C86" s="4">
+        <v>311092</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="4">
+        <v>0</v>
+      </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -4120,11 +4127,21 @@
       <c r="U86" s="2"/>
     </row>
     <row r="87" spans="1:21">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
+      <c r="A87" s="4">
+        <v>83</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C87" s="4">
+        <v>318586</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87" s="4">
+        <v>0</v>
+      </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -4143,11 +4160,19 @@
       <c r="U87" s="2"/>
     </row>
     <row r="88" spans="1:21">
-      <c r="A88" s="2"/>
+      <c r="A88" s="4">
+        <v>84</v>
+      </c>
       <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
+      <c r="C88" s="4">
+        <v>501294</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="4">
+        <v>0</v>
+      </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -4166,11 +4191,21 @@
       <c r="U88" s="2"/>
     </row>
     <row r="89" spans="1:21">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
+      <c r="A89" s="4">
+        <v>85</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" s="4">
+        <v>127013</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="4">
+        <v>0</v>
+      </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -4189,11 +4224,19 @@
       <c r="U89" s="2"/>
     </row>
     <row r="90" spans="1:21">
-      <c r="A90" s="2"/>
+      <c r="A90" s="4">
+        <v>86</v>
+      </c>
       <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
+      <c r="C90" s="4">
+        <v>146328</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="4">
+        <v>0</v>
+      </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -4212,11 +4255,19 @@
       <c r="U90" s="2"/>
     </row>
     <row r="91" spans="1:21">
-      <c r="A91" s="2"/>
+      <c r="A91" s="4">
+        <v>87</v>
+      </c>
       <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
+      <c r="C91" s="4">
+        <v>146328</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="4">
+        <v>0</v>
+      </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -4235,11 +4286,19 @@
       <c r="U91" s="2"/>
     </row>
     <row r="92" spans="1:21">
-      <c r="A92" s="2"/>
+      <c r="A92" s="4">
+        <v>88</v>
+      </c>
       <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
+      <c r="C92" s="4">
+        <v>146753</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="4">
+        <v>0</v>
+      </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -4258,11 +4317,21 @@
       <c r="U92" s="2"/>
     </row>
     <row r="93" spans="1:21">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
+      <c r="A93" s="4">
+        <v>89</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C93" s="4">
+        <v>146754</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="4">
+        <v>0</v>
+      </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -4281,11 +4350,21 @@
       <c r="U93" s="2"/>
     </row>
     <row r="94" spans="1:21">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
+      <c r="A94" s="4">
+        <v>90</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C94" s="4">
+        <v>144082</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="4">
+        <v>0</v>
+      </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -4304,11 +4383,21 @@
       <c r="U94" s="2"/>
     </row>
     <row r="95" spans="1:21">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
+      <c r="A95" s="4">
+        <v>91</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C95" s="4">
+        <v>361275</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="4">
+        <v>0</v>
+      </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -4327,11 +4416,19 @@
       <c r="U95" s="2"/>
     </row>
     <row r="96" spans="1:21">
-      <c r="A96" s="2"/>
+      <c r="A96" s="4">
+        <v>92</v>
+      </c>
       <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
+      <c r="C96" s="4">
+        <v>558271</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E96" s="4">
+        <v>0</v>
+      </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -7063,6 +7160,236 @@
       <c r="T214" s="2"/>
       <c r="U214" s="2"/>
     </row>
+    <row r="215" spans="1:21">
+      <c r="A215" s="2"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+      <c r="E215" s="2"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
+      <c r="J215" s="2"/>
+      <c r="K215" s="2"/>
+      <c r="L215" s="2"/>
+      <c r="M215" s="2"/>
+      <c r="N215" s="2"/>
+      <c r="O215" s="2"/>
+      <c r="P215" s="2"/>
+      <c r="Q215" s="2"/>
+      <c r="R215" s="2"/>
+      <c r="S215" s="2"/>
+      <c r="T215" s="2"/>
+      <c r="U215" s="2"/>
+    </row>
+    <row r="216" spans="1:21">
+      <c r="A216" s="2"/>
+      <c r="B216" s="2"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
+      <c r="E216" s="2"/>
+      <c r="F216" s="2"/>
+      <c r="G216" s="2"/>
+      <c r="H216" s="2"/>
+      <c r="I216" s="2"/>
+      <c r="J216" s="2"/>
+      <c r="K216" s="2"/>
+      <c r="L216" s="2"/>
+      <c r="M216" s="2"/>
+      <c r="N216" s="2"/>
+      <c r="O216" s="2"/>
+      <c r="P216" s="2"/>
+      <c r="Q216" s="2"/>
+      <c r="R216" s="2"/>
+      <c r="S216" s="2"/>
+      <c r="T216" s="2"/>
+      <c r="U216" s="2"/>
+    </row>
+    <row r="217" spans="1:21">
+      <c r="A217" s="2"/>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
+      <c r="E217" s="2"/>
+      <c r="F217" s="2"/>
+      <c r="G217" s="2"/>
+      <c r="H217" s="2"/>
+      <c r="I217" s="2"/>
+      <c r="J217" s="2"/>
+      <c r="K217" s="2"/>
+      <c r="L217" s="2"/>
+      <c r="M217" s="2"/>
+      <c r="N217" s="2"/>
+      <c r="O217" s="2"/>
+      <c r="P217" s="2"/>
+      <c r="Q217" s="2"/>
+      <c r="R217" s="2"/>
+      <c r="S217" s="2"/>
+      <c r="T217" s="2"/>
+      <c r="U217" s="2"/>
+    </row>
+    <row r="218" spans="1:21">
+      <c r="A218" s="2"/>
+      <c r="B218" s="2"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
+      <c r="E218" s="2"/>
+      <c r="F218" s="2"/>
+      <c r="G218" s="2"/>
+      <c r="H218" s="2"/>
+      <c r="I218" s="2"/>
+      <c r="J218" s="2"/>
+      <c r="K218" s="2"/>
+      <c r="L218" s="2"/>
+      <c r="M218" s="2"/>
+      <c r="N218" s="2"/>
+      <c r="O218" s="2"/>
+      <c r="P218" s="2"/>
+      <c r="Q218" s="2"/>
+      <c r="R218" s="2"/>
+      <c r="S218" s="2"/>
+      <c r="T218" s="2"/>
+      <c r="U218" s="2"/>
+    </row>
+    <row r="219" spans="1:21">
+      <c r="A219" s="2"/>
+      <c r="B219" s="2"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
+      <c r="E219" s="2"/>
+      <c r="F219" s="2"/>
+      <c r="G219" s="2"/>
+      <c r="H219" s="2"/>
+      <c r="I219" s="2"/>
+      <c r="J219" s="2"/>
+      <c r="K219" s="2"/>
+      <c r="L219" s="2"/>
+      <c r="M219" s="2"/>
+      <c r="N219" s="2"/>
+      <c r="O219" s="2"/>
+      <c r="P219" s="2"/>
+      <c r="Q219" s="2"/>
+      <c r="R219" s="2"/>
+      <c r="S219" s="2"/>
+      <c r="T219" s="2"/>
+      <c r="U219" s="2"/>
+    </row>
+    <row r="220" spans="1:21">
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+      <c r="J220" s="2"/>
+      <c r="K220" s="2"/>
+      <c r="L220" s="2"/>
+      <c r="M220" s="2"/>
+      <c r="N220" s="2"/>
+      <c r="O220" s="2"/>
+      <c r="P220" s="2"/>
+      <c r="Q220" s="2"/>
+      <c r="R220" s="2"/>
+      <c r="S220" s="2"/>
+      <c r="T220" s="2"/>
+      <c r="U220" s="2"/>
+    </row>
+    <row r="221" spans="1:21">
+      <c r="A221" s="2"/>
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
+      <c r="J221" s="2"/>
+      <c r="K221" s="2"/>
+      <c r="L221" s="2"/>
+      <c r="M221" s="2"/>
+      <c r="N221" s="2"/>
+      <c r="O221" s="2"/>
+      <c r="P221" s="2"/>
+      <c r="Q221" s="2"/>
+      <c r="R221" s="2"/>
+      <c r="S221" s="2"/>
+      <c r="T221" s="2"/>
+      <c r="U221" s="2"/>
+    </row>
+    <row r="222" spans="1:21">
+      <c r="A222" s="2"/>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
+      <c r="J222" s="2"/>
+      <c r="K222" s="2"/>
+      <c r="L222" s="2"/>
+      <c r="M222" s="2"/>
+      <c r="N222" s="2"/>
+      <c r="O222" s="2"/>
+      <c r="P222" s="2"/>
+      <c r="Q222" s="2"/>
+      <c r="R222" s="2"/>
+      <c r="S222" s="2"/>
+      <c r="T222" s="2"/>
+      <c r="U222" s="2"/>
+    </row>
+    <row r="223" spans="1:21">
+      <c r="A223" s="2"/>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+      <c r="J223" s="2"/>
+      <c r="K223" s="2"/>
+      <c r="L223" s="2"/>
+      <c r="M223" s="2"/>
+      <c r="N223" s="2"/>
+      <c r="O223" s="2"/>
+      <c r="P223" s="2"/>
+      <c r="Q223" s="2"/>
+      <c r="R223" s="2"/>
+      <c r="S223" s="2"/>
+      <c r="T223" s="2"/>
+      <c r="U223" s="2"/>
+    </row>
+    <row r="224" spans="1:21">
+      <c r="A224" s="2"/>
+      <c r="B224" s="2"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
+      <c r="E224" s="2"/>
+      <c r="F224" s="2"/>
+      <c r="G224" s="2"/>
+      <c r="H224" s="2"/>
+      <c r="I224" s="2"/>
+      <c r="J224" s="2"/>
+      <c r="K224" s="2"/>
+      <c r="L224" s="2"/>
+      <c r="M224" s="2"/>
+      <c r="N224" s="2"/>
+      <c r="O224" s="2"/>
+      <c r="P224" s="2"/>
+      <c r="Q224" s="2"/>
+      <c r="R224" s="2"/>
+      <c r="S224" s="2"/>
+      <c r="T224" s="2"/>
+      <c r="U224" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/rp/Excel/Effects_特效.xlsx
+++ b/rp/Excel/Effects_特效.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12060" tabRatio="500"/>
+    <workbookView windowHeight="17655" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="50">
   <si>
     <t>Int</t>
   </si>
@@ -62,9 +62,6 @@
   </si>
   <si>
     <t>0|0|0|0|0|0|1|1|1</t>
-  </si>
-  <si>
-    <t>0|0|100|0|0|0|0.1|0.02|0.1</t>
   </si>
   <si>
     <t>广告牌</t>
@@ -1372,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U224"/>
+  <dimension ref="A1:U223"/>
   <sheetFormatPr defaultColWidth="12.0666666666667" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="12.0666666666667" style="1"/>
@@ -1624,10 +1621,10 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="4">
-        <v>688276</v>
+        <v>556585</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
@@ -1655,7 +1652,7 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="4">
-        <v>556585</v>
+        <v>674918</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
@@ -1686,7 +1683,7 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="4">
-        <v>674918</v>
+        <v>565350</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
@@ -1717,7 +1714,7 @@
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="4">
-        <v>565350</v>
+        <v>567138</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -1748,7 +1745,7 @@
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="4">
-        <v>567138</v>
+        <v>567139</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -1779,7 +1776,7 @@
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="4">
-        <v>567139</v>
+        <v>525387</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -1810,7 +1807,7 @@
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="4">
-        <v>525387</v>
+        <v>501310</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1839,12 +1836,14 @@
       <c r="A16" s="4">
         <v>12</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C16" s="4">
-        <v>501310</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>10</v>
+        <v>57202</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1871,13 +1870,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" s="4">
-        <v>57202</v>
+        <v>365194</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
@@ -1904,13 +1903,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="4">
-        <v>365194</v>
+        <v>28451</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -1936,14 +1935,14 @@
       <c r="A19" s="4">
         <v>15</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>16</v>
+      <c r="B19" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="C19" s="4">
-        <v>28451</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>17</v>
+        <v>526080</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -1969,14 +1968,12 @@
       <c r="A20" s="4">
         <v>16</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="6"/>
+      <c r="C20" s="4">
+        <v>464265</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C20" s="4">
-        <v>526080</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="E20" s="4">
         <v>0</v>
@@ -2004,10 +2001,10 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="4">
-        <v>464265</v>
+        <v>266517</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21" s="4">
         <v>0</v>
@@ -2035,10 +2032,10 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="4">
-        <v>266517</v>
+        <v>266518</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
@@ -2066,10 +2063,10 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="4">
-        <v>266518</v>
+        <v>266519</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -2097,10 +2094,10 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="4">
-        <v>266519</v>
+        <v>266520</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -2128,10 +2125,10 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="4">
-        <v>266520</v>
+        <v>266521</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -2159,7 +2156,7 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="4">
-        <v>266521</v>
+        <v>439411</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>19</v>
@@ -2190,10 +2187,10 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="4">
-        <v>439411</v>
+        <v>484531</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E27" s="4">
         <v>0</v>
@@ -2221,7 +2218,7 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="4">
-        <v>484531</v>
+        <v>144088</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
@@ -2252,10 +2249,10 @@
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="4">
-        <v>144088</v>
+        <v>439415</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -2283,9 +2280,9 @@
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="4">
-        <v>439415</v>
-      </c>
-      <c r="D30" s="2" t="s">
+        <v>144093</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E30" s="4">
@@ -2314,9 +2311,9 @@
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="4">
-        <v>144093</v>
-      </c>
-      <c r="D31" s="5" t="s">
+        <v>326212</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E31" s="4">
@@ -2345,10 +2342,10 @@
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="4">
-        <v>326212</v>
+        <v>326224</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
@@ -2376,10 +2373,10 @@
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="4">
-        <v>326224</v>
+        <v>383667</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E33" s="4">
         <v>0</v>
@@ -2407,10 +2404,10 @@
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="4">
-        <v>383667</v>
+        <v>383676</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -2438,10 +2435,10 @@
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="4">
-        <v>383676</v>
+        <v>386040</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -2469,10 +2466,10 @@
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="4">
-        <v>386040</v>
+        <v>394667</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -2500,10 +2497,10 @@
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="4">
-        <v>394667</v>
+        <v>394678</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -2529,12 +2526,14 @@
       <c r="A38" s="4">
         <v>34</v>
       </c>
-      <c r="B38" s="6"/>
+      <c r="B38" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="C38" s="4">
-        <v>394678</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>23</v>
+        <v>220840</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
@@ -2556,15 +2555,13 @@
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" ht="17.25" spans="1:21">
       <c r="A39" s="4">
         <v>35</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="4">
-        <v>220840</v>
+      <c r="B39" s="2"/>
+      <c r="C39" s="7">
+        <v>485354</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>25</v>
@@ -2589,16 +2586,18 @@
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
     </row>
-    <row r="40" ht="17.25" spans="1:21">
+    <row r="40" spans="1:21">
       <c r="A40" s="4">
         <v>36</v>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="7">
-        <v>485354</v>
+      <c r="B40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" s="4">
+        <v>220841</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
@@ -2625,13 +2624,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="4">
+        <v>220842</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C41" s="4">
-        <v>220841</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
@@ -2657,14 +2656,14 @@
       <c r="A42" s="4">
         <v>38</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="4">
+        <v>220843</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C42" s="4">
-        <v>220842</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
@@ -2690,14 +2689,14 @@
       <c r="A43" s="4">
         <v>39</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="4">
+        <v>220844</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C43" s="4">
-        <v>220843</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
@@ -2724,13 +2723,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" s="4">
+        <v>220845</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C44" s="4">
-        <v>220844</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
@@ -2756,14 +2755,14 @@
       <c r="A45" s="4">
         <v>41</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" s="4">
+        <v>220846</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C45" s="4">
-        <v>220845</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -2789,14 +2788,14 @@
       <c r="A46" s="4">
         <v>42</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" s="4">
+        <v>220847</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C46" s="4">
-        <v>220846</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
@@ -2823,13 +2822,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="4">
+        <v>220848</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C47" s="4">
-        <v>220847</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E47" s="4">
         <v>0</v>
@@ -2855,14 +2854,14 @@
       <c r="A48" s="4">
         <v>44</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="4">
+        <v>220849</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C48" s="4">
-        <v>220848</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E48" s="4">
         <v>0</v>
@@ -2888,14 +2887,14 @@
       <c r="A49" s="4">
         <v>45</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" s="4">
+        <v>220850</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C49" s="4">
-        <v>220849</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -2922,13 +2921,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="4">
+        <v>220851</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C50" s="4">
-        <v>220850</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -2954,14 +2953,14 @@
       <c r="A51" s="4">
         <v>47</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" s="4">
+        <v>220041</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C51" s="4">
-        <v>220851</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -2987,14 +2986,14 @@
       <c r="A52" s="4">
         <v>48</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" s="4">
+        <v>220469</v>
+      </c>
+      <c r="D52" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C52" s="4">
-        <v>220041</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -3021,13 +3020,13 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C53" s="4">
-        <v>220469</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>25</v>
+        <v>31645</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E53" s="4">
         <v>0</v>
@@ -3057,7 +3056,7 @@
         <v>27</v>
       </c>
       <c r="C54" s="4">
-        <v>31645</v>
+        <v>4366</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
@@ -3090,7 +3089,7 @@
         <v>28</v>
       </c>
       <c r="C55" s="4">
-        <v>4366</v>
+        <v>4367</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
@@ -3123,7 +3122,7 @@
         <v>29</v>
       </c>
       <c r="C56" s="4">
-        <v>4367</v>
+        <v>4368</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>10</v>
@@ -3152,14 +3151,12 @@
       <c r="A57" s="4">
         <v>53</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="2"/>
+      <c r="C57" s="4">
+        <v>144084</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C57" s="4">
-        <v>4368</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
@@ -3187,10 +3184,10 @@
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="4">
-        <v>144084</v>
+        <v>146786</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E58" s="4">
         <v>0</v>
@@ -3218,10 +3215,10 @@
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="4">
-        <v>146786</v>
+        <v>144083</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E59" s="4">
         <v>0</v>
@@ -3247,12 +3244,14 @@
       <c r="A60" s="4">
         <v>56</v>
       </c>
-      <c r="B60" s="2"/>
+      <c r="B60" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C60" s="4">
-        <v>144083</v>
+        <v>32240</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E60" s="4">
         <v>0</v>
@@ -3279,10 +3278,10 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C61" s="4">
-        <v>32240</v>
+        <v>59956</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
@@ -3315,7 +3314,7 @@
         <v>32</v>
       </c>
       <c r="C62" s="4">
-        <v>59956</v>
+        <v>73402</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
@@ -3348,7 +3347,7 @@
         <v>33</v>
       </c>
       <c r="C63" s="4">
-        <v>73402</v>
+        <v>88762</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
@@ -3378,10 +3377,10 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C64" s="4">
-        <v>88762</v>
+        <v>88773</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
@@ -3414,7 +3413,7 @@
         <v>34</v>
       </c>
       <c r="C65" s="4">
-        <v>88773</v>
+        <v>89073</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
@@ -3447,7 +3446,7 @@
         <v>35</v>
       </c>
       <c r="C66" s="4">
-        <v>89073</v>
+        <v>89109</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
@@ -3477,10 +3476,10 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C67" s="4">
-        <v>89109</v>
+        <v>89111</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>10</v>
@@ -3510,10 +3509,10 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C68" s="4">
-        <v>89111</v>
+        <v>89112</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
@@ -3546,7 +3545,7 @@
         <v>36</v>
       </c>
       <c r="C69" s="4">
-        <v>89112</v>
+        <v>89122</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>10</v>
@@ -3579,7 +3578,7 @@
         <v>37</v>
       </c>
       <c r="C70" s="4">
-        <v>89122</v>
+        <v>113903</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>10</v>
@@ -3609,10 +3608,10 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C71" s="4">
-        <v>113903</v>
+        <v>113913</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
@@ -3642,10 +3641,10 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C72" s="4">
-        <v>113913</v>
+        <v>113907</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
@@ -3678,7 +3677,7 @@
         <v>39</v>
       </c>
       <c r="C73" s="4">
-        <v>113907</v>
+        <v>119917</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
@@ -3708,10 +3707,10 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C74" s="4">
-        <v>119917</v>
+        <v>130776</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>10</v>
@@ -3744,7 +3743,7 @@
         <v>40</v>
       </c>
       <c r="C75" s="4">
-        <v>130776</v>
+        <v>141655</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
@@ -3774,10 +3773,10 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C76" s="4">
-        <v>141655</v>
+        <v>141657</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>10</v>
@@ -3810,7 +3809,7 @@
         <v>41</v>
       </c>
       <c r="C77" s="4">
-        <v>141657</v>
+        <v>142753</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>10</v>
@@ -3840,10 +3839,10 @@
         <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C78" s="4">
-        <v>142753</v>
+        <v>142751</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>10</v>
@@ -3873,10 +3872,10 @@
         <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C79" s="4">
-        <v>142751</v>
+        <v>142951</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>10</v>
@@ -3906,10 +3905,10 @@
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C80" s="4">
-        <v>142951</v>
+        <v>156399</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>10</v>
@@ -3938,11 +3937,9 @@
       <c r="A81" s="4">
         <v>77</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B81" s="2"/>
       <c r="C81" s="4">
-        <v>156399</v>
+        <v>157113</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>10</v>
@@ -3973,7 +3970,7 @@
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="4">
-        <v>157113</v>
+        <v>157118</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>10</v>
@@ -4004,7 +4001,7 @@
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="4">
-        <v>157118</v>
+        <v>157119</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>10</v>
@@ -4033,9 +4030,11 @@
       <c r="A84" s="4">
         <v>80</v>
       </c>
-      <c r="B84" s="2"/>
+      <c r="B84" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="C84" s="4">
-        <v>157119</v>
+        <v>271322</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>10</v>
@@ -4068,7 +4067,7 @@
         <v>44</v>
       </c>
       <c r="C85" s="4">
-        <v>271322</v>
+        <v>311092</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>10</v>
@@ -4101,7 +4100,7 @@
         <v>45</v>
       </c>
       <c r="C86" s="4">
-        <v>311092</v>
+        <v>318586</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>10</v>
@@ -4130,11 +4129,9 @@
       <c r="A87" s="4">
         <v>83</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="B87" s="2"/>
       <c r="C87" s="4">
-        <v>318586</v>
+        <v>501294</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>10</v>
@@ -4163,9 +4160,11 @@
       <c r="A88" s="4">
         <v>84</v>
       </c>
-      <c r="B88" s="2"/>
+      <c r="B88" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C88" s="4">
-        <v>501294</v>
+        <v>127013</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>10</v>
@@ -4194,11 +4193,9 @@
       <c r="A89" s="4">
         <v>85</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="B89" s="2"/>
       <c r="C89" s="4">
-        <v>127013</v>
+        <v>146328</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>10</v>
@@ -4260,7 +4257,7 @@
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="4">
-        <v>146328</v>
+        <v>146753</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>10</v>
@@ -4289,9 +4286,11 @@
       <c r="A92" s="4">
         <v>88</v>
       </c>
-      <c r="B92" s="2"/>
+      <c r="B92" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="C92" s="4">
-        <v>146753</v>
+        <v>146754</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>10</v>
@@ -4324,7 +4323,7 @@
         <v>47</v>
       </c>
       <c r="C93" s="4">
-        <v>146754</v>
+        <v>144082</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>10</v>
@@ -4357,7 +4356,7 @@
         <v>48</v>
       </c>
       <c r="C94" s="4">
-        <v>144082</v>
+        <v>361275</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>10</v>
@@ -4386,14 +4385,12 @@
       <c r="A95" s="4">
         <v>91</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="2"/>
+      <c r="C95" s="4">
+        <v>558271</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C95" s="4">
-        <v>361275</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="E95" s="4">
         <v>0</v>
@@ -4416,19 +4413,11 @@
       <c r="U95" s="2"/>
     </row>
     <row r="96" spans="1:21">
-      <c r="A96" s="4">
-        <v>92</v>
-      </c>
+      <c r="A96" s="2"/>
       <c r="B96" s="2"/>
-      <c r="C96" s="4">
-        <v>558271</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E96" s="4">
-        <v>0</v>
-      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -7367,29 +7356,6 @@
       <c r="T223" s="2"/>
       <c r="U223" s="2"/>
     </row>
-    <row r="224" spans="1:21">
-      <c r="A224" s="2"/>
-      <c r="B224" s="2"/>
-      <c r="C224" s="2"/>
-      <c r="D224" s="2"/>
-      <c r="E224" s="2"/>
-      <c r="F224" s="2"/>
-      <c r="G224" s="2"/>
-      <c r="H224" s="2"/>
-      <c r="I224" s="2"/>
-      <c r="J224" s="2"/>
-      <c r="K224" s="2"/>
-      <c r="L224" s="2"/>
-      <c r="M224" s="2"/>
-      <c r="N224" s="2"/>
-      <c r="O224" s="2"/>
-      <c r="P224" s="2"/>
-      <c r="Q224" s="2"/>
-      <c r="R224" s="2"/>
-      <c r="S224" s="2"/>
-      <c r="T224" s="2"/>
-      <c r="U224" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/rp/Excel/Effects_特效.xlsx
+++ b/rp/Excel/Effects_特效.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="50">
   <si>
     <t>Int</t>
   </si>
@@ -1369,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U223"/>
+  <dimension ref="A1:U220"/>
   <sheetFormatPr defaultColWidth="12.0666666666667" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="12.0666666666667" style="1"/>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>687895</v>
+        <v>556585</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="4">
-        <v>687897</v>
+        <v>674918</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="4">
-        <v>687899</v>
+        <v>565350</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="4">
-        <v>556585</v>
+        <v>567138</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="4">
-        <v>674918</v>
+        <v>567139</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="4">
-        <v>565350</v>
+        <v>525387</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="4">
-        <v>567138</v>
+        <v>501310</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -1743,12 +1743,14 @@
       <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C13" s="4">
-        <v>567139</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>10</v>
+        <v>57202</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
@@ -1774,12 +1776,14 @@
       <c r="A14" s="4">
         <v>10</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C14" s="4">
-        <v>525387</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
+        <v>365194</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -1805,12 +1809,14 @@
       <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C15" s="4">
-        <v>501310</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
+        <v>28451</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -1836,14 +1842,14 @@
       <c r="A16" s="4">
         <v>12</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>11</v>
+      <c r="B16" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="C16" s="4">
-        <v>57202</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>12</v>
+        <v>526080</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1869,14 +1875,12 @@
       <c r="A17" s="4">
         <v>13</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="B17" s="6"/>
       <c r="C17" s="4">
-        <v>365194</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>14</v>
+        <v>464265</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
@@ -1902,14 +1906,12 @@
       <c r="A18" s="4">
         <v>14</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B18" s="6"/>
       <c r="C18" s="4">
-        <v>28451</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>16</v>
+        <v>266517</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -1935,14 +1937,12 @@
       <c r="A19" s="4">
         <v>15</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="B19" s="6"/>
       <c r="C19" s="4">
-        <v>526080</v>
+        <v>266518</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="4">
-        <v>464265</v>
+        <v>266519</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="4">
-        <v>266517</v>
+        <v>266520</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="4">
-        <v>266518</v>
+        <v>266521</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
@@ -2063,10 +2063,10 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="4">
-        <v>266519</v>
+        <v>439411</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -2094,10 +2094,10 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="4">
-        <v>266520</v>
+        <v>484531</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -2125,10 +2125,10 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="4">
-        <v>266521</v>
+        <v>144088</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -2156,10 +2156,10 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="4">
-        <v>439411</v>
+        <v>439415</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -2187,10 +2187,10 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="4">
-        <v>484531</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>10</v>
+        <v>144093</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="E27" s="4">
         <v>0</v>
@@ -2218,10 +2218,10 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="4">
-        <v>144088</v>
+        <v>326212</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -2249,10 +2249,10 @@
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="4">
-        <v>439415</v>
+        <v>326224</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -2280,10 +2280,10 @@
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="4">
-        <v>144093</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>21</v>
+        <v>383667</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="4">
-        <v>326212</v>
+        <v>383676</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>22</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="4">
-        <v>326224</v>
+        <v>386040</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>22</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="4">
-        <v>383667</v>
+        <v>394667</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>22</v>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="4">
-        <v>383676</v>
+        <v>394678</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>22</v>
@@ -2433,12 +2433,14 @@
       <c r="A35" s="4">
         <v>31</v>
       </c>
-      <c r="B35" s="6"/>
+      <c r="B35" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="C35" s="4">
-        <v>386040</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>22</v>
+        <v>220840</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -2460,16 +2462,16 @@
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" ht="17.25" spans="1:21">
       <c r="A36" s="4">
         <v>32</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="4">
-        <v>394667</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>22</v>
+      <c r="B36" s="2"/>
+      <c r="C36" s="7">
+        <v>485354</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -2495,12 +2497,14 @@
       <c r="A37" s="4">
         <v>33</v>
       </c>
-      <c r="B37" s="6"/>
+      <c r="B37" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="C37" s="4">
-        <v>394678</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>22</v>
+        <v>220841</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -2526,11 +2530,11 @@
       <c r="A38" s="4">
         <v>34</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C38" s="4">
-        <v>220840</v>
+        <v>220842</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>24</v>
@@ -2555,16 +2559,18 @@
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
-    <row r="39" ht="17.25" spans="1:21">
+    <row r="39" spans="1:21">
       <c r="A39" s="4">
         <v>35</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="7">
-        <v>485354</v>
+      <c r="B39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" s="4">
+        <v>220843</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -2594,7 +2600,7 @@
         <v>23</v>
       </c>
       <c r="C40" s="4">
-        <v>220841</v>
+        <v>220844</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>24</v>
@@ -2627,7 +2633,7 @@
         <v>23</v>
       </c>
       <c r="C41" s="4">
-        <v>220842</v>
+        <v>220845</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>24</v>
@@ -2660,7 +2666,7 @@
         <v>23</v>
       </c>
       <c r="C42" s="4">
-        <v>220843</v>
+        <v>220846</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>24</v>
@@ -2693,7 +2699,7 @@
         <v>23</v>
       </c>
       <c r="C43" s="4">
-        <v>220844</v>
+        <v>220847</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>24</v>
@@ -2726,7 +2732,7 @@
         <v>23</v>
       </c>
       <c r="C44" s="4">
-        <v>220845</v>
+        <v>220848</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>24</v>
@@ -2759,7 +2765,7 @@
         <v>23</v>
       </c>
       <c r="C45" s="4">
-        <v>220846</v>
+        <v>220849</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>24</v>
@@ -2792,7 +2798,7 @@
         <v>23</v>
       </c>
       <c r="C46" s="4">
-        <v>220847</v>
+        <v>220850</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>24</v>
@@ -2825,7 +2831,7 @@
         <v>23</v>
       </c>
       <c r="C47" s="4">
-        <v>220848</v>
+        <v>220851</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>24</v>
@@ -2858,7 +2864,7 @@
         <v>23</v>
       </c>
       <c r="C48" s="4">
-        <v>220849</v>
+        <v>220041</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>24</v>
@@ -2891,7 +2897,7 @@
         <v>23</v>
       </c>
       <c r="C49" s="4">
-        <v>220850</v>
+        <v>220469</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>24</v>
@@ -2921,13 +2927,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C50" s="4">
-        <v>220851</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>24</v>
+        <v>31645</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -2953,14 +2959,14 @@
       <c r="A51" s="4">
         <v>47</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>23</v>
+      <c r="B51" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C51" s="4">
-        <v>220041</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>24</v>
+        <v>4366</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -2987,13 +2993,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C52" s="4">
-        <v>220469</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>24</v>
+        <v>4367</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -3020,10 +3026,10 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C53" s="4">
-        <v>31645</v>
+        <v>4368</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
@@ -3052,14 +3058,12 @@
       <c r="A54" s="4">
         <v>50</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="B54" s="2"/>
       <c r="C54" s="4">
-        <v>4366</v>
+        <v>144084</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E54" s="4">
         <v>0</v>
@@ -3085,11 +3089,9 @@
       <c r="A55" s="4">
         <v>51</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B55" s="2"/>
       <c r="C55" s="4">
-        <v>4367</v>
+        <v>146786</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
@@ -3118,14 +3120,12 @@
       <c r="A56" s="4">
         <v>52</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B56" s="2"/>
       <c r="C56" s="4">
-        <v>4368</v>
+        <v>144083</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E56" s="4">
         <v>0</v>
@@ -3151,12 +3151,14 @@
       <c r="A57" s="4">
         <v>53</v>
       </c>
-      <c r="B57" s="2"/>
+      <c r="B57" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C57" s="4">
-        <v>144084</v>
+        <v>32240</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
@@ -3182,9 +3184,11 @@
       <c r="A58" s="4">
         <v>54</v>
       </c>
-      <c r="B58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C58" s="4">
-        <v>146786</v>
+        <v>59956</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>10</v>
@@ -3213,12 +3217,14 @@
       <c r="A59" s="4">
         <v>55</v>
       </c>
-      <c r="B59" s="2"/>
+      <c r="B59" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C59" s="4">
-        <v>144083</v>
+        <v>73402</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E59" s="4">
         <v>0</v>
@@ -3245,10 +3251,10 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C60" s="4">
-        <v>32240</v>
+        <v>88762</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>10</v>
@@ -3278,10 +3284,10 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C61" s="4">
-        <v>59956</v>
+        <v>88773</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
@@ -3311,10 +3317,10 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C62" s="4">
-        <v>73402</v>
+        <v>89073</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
@@ -3344,10 +3350,10 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C63" s="4">
-        <v>88762</v>
+        <v>89109</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
@@ -3377,10 +3383,10 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C64" s="4">
-        <v>88773</v>
+        <v>89111</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
@@ -3410,10 +3416,10 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C65" s="4">
-        <v>89073</v>
+        <v>89112</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
@@ -3443,10 +3449,10 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C66" s="4">
-        <v>89109</v>
+        <v>89122</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
@@ -3476,10 +3482,10 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C67" s="4">
-        <v>89111</v>
+        <v>113903</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>10</v>
@@ -3509,10 +3515,10 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C68" s="4">
-        <v>89112</v>
+        <v>113913</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
@@ -3542,10 +3548,10 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C69" s="4">
-        <v>89122</v>
+        <v>113907</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>10</v>
@@ -3575,10 +3581,10 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C70" s="4">
-        <v>113903</v>
+        <v>119917</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>10</v>
@@ -3608,10 +3614,10 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C71" s="4">
-        <v>113913</v>
+        <v>130776</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
@@ -3641,10 +3647,10 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C72" s="4">
-        <v>113907</v>
+        <v>141655</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
@@ -3674,10 +3680,10 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C73" s="4">
-        <v>119917</v>
+        <v>141657</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
@@ -3707,10 +3713,10 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C74" s="4">
-        <v>130776</v>
+        <v>142753</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>10</v>
@@ -3740,10 +3746,10 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C75" s="4">
-        <v>141655</v>
+        <v>142751</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
@@ -3773,10 +3779,10 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C76" s="4">
-        <v>141657</v>
+        <v>142951</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>10</v>
@@ -3806,10 +3812,10 @@
         <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C77" s="4">
-        <v>142753</v>
+        <v>156399</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>10</v>
@@ -3838,11 +3844,9 @@
       <c r="A78" s="4">
         <v>74</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="B78" s="2"/>
       <c r="C78" s="4">
-        <v>142751</v>
+        <v>157113</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>10</v>
@@ -3871,11 +3875,9 @@
       <c r="A79" s="4">
         <v>75</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B79" s="2"/>
       <c r="C79" s="4">
-        <v>142951</v>
+        <v>157118</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>10</v>
@@ -3904,11 +3906,9 @@
       <c r="A80" s="4">
         <v>76</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="B80" s="2"/>
       <c r="C80" s="4">
-        <v>156399</v>
+        <v>157119</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>10</v>
@@ -3937,9 +3937,11 @@
       <c r="A81" s="4">
         <v>77</v>
       </c>
-      <c r="B81" s="2"/>
+      <c r="B81" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="C81" s="4">
-        <v>157113</v>
+        <v>271322</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>10</v>
@@ -3968,9 +3970,11 @@
       <c r="A82" s="4">
         <v>78</v>
       </c>
-      <c r="B82" s="2"/>
+      <c r="B82" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="C82" s="4">
-        <v>157118</v>
+        <v>311092</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>10</v>
@@ -3999,9 +4003,11 @@
       <c r="A83" s="4">
         <v>79</v>
       </c>
-      <c r="B83" s="2"/>
+      <c r="B83" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="C83" s="4">
-        <v>157119</v>
+        <v>318586</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>10</v>
@@ -4030,11 +4036,9 @@
       <c r="A84" s="4">
         <v>80</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="4">
-        <v>271322</v>
+        <v>501294</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>10</v>
@@ -4064,10 +4068,10 @@
         <v>81</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C85" s="4">
-        <v>311092</v>
+        <v>127013</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>10</v>
@@ -4096,11 +4100,9 @@
       <c r="A86" s="4">
         <v>82</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="B86" s="2"/>
       <c r="C86" s="4">
-        <v>318586</v>
+        <v>146328</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>10</v>
@@ -4131,7 +4133,7 @@
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="4">
-        <v>501294</v>
+        <v>146328</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>10</v>
@@ -4160,11 +4162,9 @@
       <c r="A88" s="4">
         <v>84</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B88" s="2"/>
       <c r="C88" s="4">
-        <v>127013</v>
+        <v>146753</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>10</v>
@@ -4193,9 +4193,11 @@
       <c r="A89" s="4">
         <v>85</v>
       </c>
-      <c r="B89" s="2"/>
+      <c r="B89" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="C89" s="4">
-        <v>146328</v>
+        <v>146754</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>10</v>
@@ -4224,9 +4226,11 @@
       <c r="A90" s="4">
         <v>86</v>
       </c>
-      <c r="B90" s="2"/>
+      <c r="B90" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="C90" s="4">
-        <v>146328</v>
+        <v>144082</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>10</v>
@@ -4255,9 +4259,11 @@
       <c r="A91" s="4">
         <v>87</v>
       </c>
-      <c r="B91" s="2"/>
+      <c r="B91" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="C91" s="4">
-        <v>146753</v>
+        <v>361275</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>10</v>
@@ -4286,14 +4292,12 @@
       <c r="A92" s="4">
         <v>88</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="B92" s="2"/>
       <c r="C92" s="4">
-        <v>146754</v>
+        <v>558271</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="E92" s="4">
         <v>0</v>
@@ -4316,21 +4320,11 @@
       <c r="U92" s="2"/>
     </row>
     <row r="93" spans="1:21">
-      <c r="A93" s="4">
-        <v>89</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C93" s="4">
-        <v>144082</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" s="4">
-        <v>0</v>
-      </c>
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -4349,21 +4343,11 @@
       <c r="U93" s="2"/>
     </row>
     <row r="94" spans="1:21">
-      <c r="A94" s="4">
-        <v>90</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C94" s="4">
-        <v>361275</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="4">
-        <v>0</v>
-      </c>
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -4382,19 +4366,11 @@
       <c r="U94" s="2"/>
     </row>
     <row r="95" spans="1:21">
-      <c r="A95" s="4">
-        <v>91</v>
-      </c>
+      <c r="A95" s="2"/>
       <c r="B95" s="2"/>
-      <c r="C95" s="4">
-        <v>558271</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E95" s="4">
-        <v>0</v>
-      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -7287,75 +7263,6 @@
       <c r="T220" s="2"/>
       <c r="U220" s="2"/>
     </row>
-    <row r="221" spans="1:21">
-      <c r="A221" s="2"/>
-      <c r="B221" s="2"/>
-      <c r="C221" s="2"/>
-      <c r="D221" s="2"/>
-      <c r="E221" s="2"/>
-      <c r="F221" s="2"/>
-      <c r="G221" s="2"/>
-      <c r="H221" s="2"/>
-      <c r="I221" s="2"/>
-      <c r="J221" s="2"/>
-      <c r="K221" s="2"/>
-      <c r="L221" s="2"/>
-      <c r="M221" s="2"/>
-      <c r="N221" s="2"/>
-      <c r="O221" s="2"/>
-      <c r="P221" s="2"/>
-      <c r="Q221" s="2"/>
-      <c r="R221" s="2"/>
-      <c r="S221" s="2"/>
-      <c r="T221" s="2"/>
-      <c r="U221" s="2"/>
-    </row>
-    <row r="222" spans="1:21">
-      <c r="A222" s="2"/>
-      <c r="B222" s="2"/>
-      <c r="C222" s="2"/>
-      <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
-      <c r="F222" s="2"/>
-      <c r="G222" s="2"/>
-      <c r="H222" s="2"/>
-      <c r="I222" s="2"/>
-      <c r="J222" s="2"/>
-      <c r="K222" s="2"/>
-      <c r="L222" s="2"/>
-      <c r="M222" s="2"/>
-      <c r="N222" s="2"/>
-      <c r="O222" s="2"/>
-      <c r="P222" s="2"/>
-      <c r="Q222" s="2"/>
-      <c r="R222" s="2"/>
-      <c r="S222" s="2"/>
-      <c r="T222" s="2"/>
-      <c r="U222" s="2"/>
-    </row>
-    <row r="223" spans="1:21">
-      <c r="A223" s="2"/>
-      <c r="B223" s="2"/>
-      <c r="C223" s="2"/>
-      <c r="D223" s="2"/>
-      <c r="E223" s="2"/>
-      <c r="F223" s="2"/>
-      <c r="G223" s="2"/>
-      <c r="H223" s="2"/>
-      <c r="I223" s="2"/>
-      <c r="J223" s="2"/>
-      <c r="K223" s="2"/>
-      <c r="L223" s="2"/>
-      <c r="M223" s="2"/>
-      <c r="N223" s="2"/>
-      <c r="O223" s="2"/>
-      <c r="P223" s="2"/>
-      <c r="Q223" s="2"/>
-      <c r="R223" s="2"/>
-      <c r="S223" s="2"/>
-      <c r="T223" s="2"/>
-      <c r="U223" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/rp/Excel/Effects_特效.xlsx
+++ b/rp/Excel/Effects_特效.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9015" tabRatio="500"/>
+    <workbookView windowWidth="24750" windowHeight="12060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="50">
   <si>
     <t>Int</t>
   </si>
@@ -58,10 +58,10 @@
 2-FeMale</t>
   </si>
   <si>
-    <t>0|0|0|0|0|0|1|1|1</t>
+    <t>0|0|50|0|0|0|0.1|0.1|0.1</t>
   </si>
   <si>
-    <t>0|0|150|0|0|0|1|1|1</t>
+    <t>0|0|0|0|0|0|1|1|1</t>
   </si>
   <si>
     <t>广告牌</t>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>剪纸</t>
+  </si>
+  <si>
+    <t>0|0|150|0|0|0|1|1|1</t>
   </si>
 </sst>
 </file>
@@ -1366,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U219"/>
+  <dimension ref="A1:U220"/>
   <sheetFormatPr defaultColWidth="12.0666666666667" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="12.0666666666667" style="1"/>
@@ -1494,7 +1497,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="4">
-        <v>556585</v>
+        <v>681318</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -1525,7 +1528,7 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>558271</v>
+        <v>556585</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
@@ -1556,10 +1559,10 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="4">
-        <v>565350</v>
+        <v>674918</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" s="4">
         <v>0</v>
@@ -1587,10 +1590,10 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="4">
-        <v>567138</v>
+        <v>565350</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
@@ -1618,10 +1621,10 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="4">
-        <v>567139</v>
+        <v>567138</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
@@ -1649,10 +1652,10 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="4">
-        <v>525387</v>
+        <v>567139</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4">
         <v>0</v>
@@ -1680,10 +1683,10 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="4">
-        <v>501310</v>
+        <v>525387</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4">
         <v>0</v>
@@ -1709,14 +1712,12 @@
       <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B12" s="2"/>
       <c r="C12" s="4">
-        <v>57202</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>12</v>
+        <v>501310</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -1743,13 +1744,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" s="4">
-        <v>365194</v>
+        <v>57202</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
@@ -1776,13 +1777,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" s="4">
-        <v>28451</v>
+        <v>365194</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -1808,14 +1809,14 @@
       <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>17</v>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C15" s="4">
-        <v>526080</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>28451</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -1841,12 +1842,14 @@
       <c r="A16" s="4">
         <v>12</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="C16" s="4">
-        <v>464265</v>
+        <v>526080</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1874,7 +1877,7 @@
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="4">
-        <v>266517</v>
+        <v>464265</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
@@ -1905,7 +1908,7 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="4">
-        <v>266518</v>
+        <v>266517</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
@@ -1936,7 +1939,7 @@
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="4">
-        <v>266519</v>
+        <v>266518</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
@@ -1967,7 +1970,7 @@
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="4">
-        <v>266520</v>
+        <v>266519</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
@@ -1998,7 +2001,7 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="4">
-        <v>266521</v>
+        <v>266520</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
@@ -2029,10 +2032,10 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="4">
-        <v>439411</v>
+        <v>266521</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
@@ -2060,10 +2063,10 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="4">
-        <v>484531</v>
+        <v>439411</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -2091,10 +2094,10 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="4">
-        <v>144088</v>
+        <v>484531</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -2122,10 +2125,10 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="4">
-        <v>439415</v>
+        <v>144088</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -2153,10 +2156,10 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="4">
-        <v>144093</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>21</v>
+        <v>439415</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -2184,10 +2187,10 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="4">
-        <v>326212</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>22</v>
+        <v>144093</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="E27" s="4">
         <v>0</v>
@@ -2215,7 +2218,7 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="4">
-        <v>326224</v>
+        <v>326212</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>22</v>
@@ -2246,7 +2249,7 @@
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="4">
-        <v>383667</v>
+        <v>326224</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>22</v>
@@ -2277,7 +2280,7 @@
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="4">
-        <v>383676</v>
+        <v>383667</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>22</v>
@@ -2308,7 +2311,7 @@
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="4">
-        <v>386040</v>
+        <v>383676</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>22</v>
@@ -2339,7 +2342,7 @@
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="4">
-        <v>394667</v>
+        <v>386040</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>22</v>
@@ -2370,7 +2373,7 @@
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="4">
-        <v>394678</v>
+        <v>394667</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>22</v>
@@ -2399,14 +2402,12 @@
       <c r="A34" s="4">
         <v>30</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="B34" s="6"/>
       <c r="C34" s="4">
-        <v>220840</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>24</v>
+        <v>394678</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -2428,16 +2429,18 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
     </row>
-    <row r="35" ht="17.25" spans="1:21">
+    <row r="35" spans="1:21">
       <c r="A35" s="4">
         <v>31</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="7">
-        <v>485354</v>
+      <c r="B35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="4">
+        <v>220840</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -2459,18 +2462,16 @@
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" ht="17.25" spans="1:21">
       <c r="A36" s="4">
         <v>32</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" s="4">
-        <v>220841</v>
+      <c r="B36" s="2"/>
+      <c r="C36" s="7">
+        <v>485354</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -2500,7 +2501,7 @@
         <v>23</v>
       </c>
       <c r="C37" s="4">
-        <v>220842</v>
+        <v>220841</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>24</v>
@@ -2529,11 +2530,11 @@
       <c r="A38" s="4">
         <v>34</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C38" s="4">
-        <v>220843</v>
+        <v>220842</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>24</v>
@@ -2562,11 +2563,11 @@
       <c r="A39" s="4">
         <v>35</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C39" s="4">
-        <v>220844</v>
+        <v>220843</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>24</v>
@@ -2599,7 +2600,7 @@
         <v>23</v>
       </c>
       <c r="C40" s="4">
-        <v>220845</v>
+        <v>220844</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>24</v>
@@ -2628,11 +2629,11 @@
       <c r="A41" s="4">
         <v>37</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C41" s="4">
-        <v>220846</v>
+        <v>220845</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>24</v>
@@ -2661,11 +2662,11 @@
       <c r="A42" s="4">
         <v>38</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C42" s="4">
-        <v>220847</v>
+        <v>220846</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>24</v>
@@ -2698,7 +2699,7 @@
         <v>23</v>
       </c>
       <c r="C43" s="4">
-        <v>220848</v>
+        <v>220847</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>24</v>
@@ -2727,11 +2728,11 @@
       <c r="A44" s="4">
         <v>40</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C44" s="4">
-        <v>220849</v>
+        <v>220848</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>24</v>
@@ -2760,11 +2761,11 @@
       <c r="A45" s="4">
         <v>41</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C45" s="4">
-        <v>220850</v>
+        <v>220849</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>24</v>
@@ -2797,7 +2798,7 @@
         <v>23</v>
       </c>
       <c r="C46" s="4">
-        <v>220851</v>
+        <v>220850</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>24</v>
@@ -2826,11 +2827,11 @@
       <c r="A47" s="4">
         <v>43</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C47" s="4">
-        <v>220041</v>
+        <v>220851</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>24</v>
@@ -2859,11 +2860,11 @@
       <c r="A48" s="4">
         <v>44</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C48" s="4">
-        <v>220469</v>
+        <v>220041</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>24</v>
@@ -2893,13 +2894,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C49" s="4">
-        <v>31645</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>9</v>
+        <v>220469</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -2926,13 +2927,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C50" s="4">
-        <v>4366</v>
+        <v>31645</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -2959,13 +2960,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C51" s="4">
-        <v>4367</v>
+        <v>4366</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -2992,13 +2993,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C52" s="4">
-        <v>4368</v>
+        <v>4367</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -3024,12 +3025,14 @@
       <c r="A53" s="4">
         <v>49</v>
       </c>
-      <c r="B53" s="2"/>
+      <c r="B53" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="C53" s="4">
-        <v>144084</v>
+        <v>4368</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E53" s="4">
         <v>0</v>
@@ -3057,10 +3060,10 @@
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="4">
-        <v>146786</v>
+        <v>144084</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E54" s="4">
         <v>0</v>
@@ -3088,10 +3091,10 @@
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="4">
-        <v>144083</v>
+        <v>146786</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E55" s="4">
         <v>0</v>
@@ -3117,14 +3120,12 @@
       <c r="A56" s="4">
         <v>52</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B56" s="2"/>
       <c r="C56" s="4">
-        <v>32240</v>
+        <v>144083</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E56" s="4">
         <v>0</v>
@@ -3154,10 +3155,10 @@
         <v>31</v>
       </c>
       <c r="C57" s="4">
-        <v>59956</v>
+        <v>32240</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
@@ -3184,13 +3185,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C58" s="4">
-        <v>73402</v>
+        <v>59956</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E58" s="4">
         <v>0</v>
@@ -3217,13 +3218,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C59" s="4">
-        <v>88762</v>
+        <v>73402</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E59" s="4">
         <v>0</v>
@@ -3253,10 +3254,10 @@
         <v>33</v>
       </c>
       <c r="C60" s="4">
-        <v>88773</v>
+        <v>88762</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E60" s="4">
         <v>0</v>
@@ -3283,13 +3284,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C61" s="4">
-        <v>89073</v>
+        <v>88773</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E61" s="4">
         <v>0</v>
@@ -3316,13 +3317,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C62" s="4">
-        <v>89109</v>
+        <v>89073</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E62" s="4">
         <v>0</v>
@@ -3352,10 +3353,10 @@
         <v>35</v>
       </c>
       <c r="C63" s="4">
-        <v>89111</v>
+        <v>89109</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E63" s="4">
         <v>0</v>
@@ -3385,10 +3386,10 @@
         <v>35</v>
       </c>
       <c r="C64" s="4">
-        <v>89112</v>
+        <v>89111</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E64" s="4">
         <v>0</v>
@@ -3415,13 +3416,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C65" s="4">
-        <v>89122</v>
+        <v>89112</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E65" s="4">
         <v>0</v>
@@ -3448,13 +3449,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C66" s="4">
-        <v>113903</v>
+        <v>89122</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E66" s="4">
         <v>0</v>
@@ -3481,13 +3482,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C67" s="4">
-        <v>113913</v>
+        <v>113903</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E67" s="4">
         <v>0</v>
@@ -3514,13 +3515,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C68" s="4">
-        <v>113907</v>
+        <v>113913</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E68" s="4">
         <v>0</v>
@@ -3547,13 +3548,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C69" s="4">
-        <v>119917</v>
+        <v>113907</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E69" s="4">
         <v>0</v>
@@ -3583,10 +3584,10 @@
         <v>39</v>
       </c>
       <c r="C70" s="4">
-        <v>130776</v>
+        <v>119917</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E70" s="4">
         <v>0</v>
@@ -3613,13 +3614,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C71" s="4">
-        <v>141655</v>
+        <v>130776</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E71" s="4">
         <v>0</v>
@@ -3649,10 +3650,10 @@
         <v>40</v>
       </c>
       <c r="C72" s="4">
-        <v>141657</v>
+        <v>141655</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E72" s="4">
         <v>0</v>
@@ -3679,13 +3680,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C73" s="4">
-        <v>142753</v>
+        <v>141657</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E73" s="4">
         <v>0</v>
@@ -3715,10 +3716,10 @@
         <v>41</v>
       </c>
       <c r="C74" s="4">
-        <v>142751</v>
+        <v>142753</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E74" s="4">
         <v>0</v>
@@ -3745,13 +3746,13 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C75" s="4">
-        <v>142951</v>
+        <v>142751</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75" s="4">
         <v>0</v>
@@ -3778,13 +3779,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C76" s="4">
-        <v>156399</v>
+        <v>142951</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" s="4">
         <v>0</v>
@@ -3810,12 +3811,14 @@
       <c r="A77" s="4">
         <v>73</v>
       </c>
-      <c r="B77" s="2"/>
+      <c r="B77" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C77" s="4">
-        <v>157113</v>
+        <v>156399</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E77" s="4">
         <v>0</v>
@@ -3843,10 +3846,10 @@
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="4">
-        <v>157118</v>
+        <v>157113</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E78" s="4">
         <v>0</v>
@@ -3874,10 +3877,10 @@
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="4">
-        <v>157119</v>
+        <v>157118</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E79" s="4">
         <v>0</v>
@@ -3903,14 +3906,12 @@
       <c r="A80" s="4">
         <v>76</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B80" s="2"/>
       <c r="C80" s="4">
-        <v>271322</v>
+        <v>157119</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E80" s="4">
         <v>0</v>
@@ -3937,13 +3938,13 @@
         <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C81" s="4">
-        <v>311092</v>
+        <v>271322</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E81" s="4">
         <v>0</v>
@@ -3970,13 +3971,13 @@
         <v>78</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C82" s="4">
-        <v>318586</v>
+        <v>311092</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E82" s="4">
         <v>0</v>
@@ -4002,12 +4003,14 @@
       <c r="A83" s="4">
         <v>79</v>
       </c>
-      <c r="B83" s="2"/>
+      <c r="B83" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="C83" s="4">
-        <v>501294</v>
+        <v>318586</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E83" s="4">
         <v>0</v>
@@ -4033,14 +4036,12 @@
       <c r="A84" s="4">
         <v>80</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="4">
-        <v>127013</v>
+        <v>501294</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E84" s="4">
         <v>0</v>
@@ -4066,12 +4067,14 @@
       <c r="A85" s="4">
         <v>81</v>
       </c>
-      <c r="B85" s="2"/>
+      <c r="B85" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C85" s="4">
-        <v>146328</v>
+        <v>127013</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E85" s="4">
         <v>0</v>
@@ -4102,7 +4105,7 @@
         <v>146328</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E86" s="4">
         <v>0</v>
@@ -4130,10 +4133,10 @@
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="4">
-        <v>146753</v>
+        <v>146328</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E87" s="4">
         <v>0</v>
@@ -4159,14 +4162,12 @@
       <c r="A88" s="4">
         <v>84</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="B88" s="2"/>
       <c r="C88" s="4">
-        <v>146754</v>
+        <v>146753</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E88" s="4">
         <v>0</v>
@@ -4193,13 +4194,13 @@
         <v>85</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C89" s="4">
-        <v>144082</v>
+        <v>146754</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E89" s="4">
         <v>0</v>
@@ -4226,13 +4227,13 @@
         <v>86</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C90" s="4">
-        <v>361275</v>
+        <v>144082</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E90" s="4">
         <v>0</v>
@@ -4255,11 +4256,21 @@
       <c r="U90" s="2"/>
     </row>
     <row r="91" spans="1:21">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
+      <c r="A91" s="4">
+        <v>87</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C91" s="4">
+        <v>361275</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="4">
+        <v>0</v>
+      </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -4278,11 +4289,19 @@
       <c r="U91" s="2"/>
     </row>
     <row r="92" spans="1:21">
-      <c r="A92" s="2"/>
+      <c r="A92" s="4">
+        <v>88</v>
+      </c>
       <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
+      <c r="C92" s="4">
+        <v>558271</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E92" s="4">
+        <v>0</v>
+      </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -7221,6 +7240,29 @@
       <c r="T219" s="2"/>
       <c r="U219" s="2"/>
     </row>
+    <row r="220" spans="1:21">
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+      <c r="J220" s="2"/>
+      <c r="K220" s="2"/>
+      <c r="L220" s="2"/>
+      <c r="M220" s="2"/>
+      <c r="N220" s="2"/>
+      <c r="O220" s="2"/>
+      <c r="P220" s="2"/>
+      <c r="Q220" s="2"/>
+      <c r="R220" s="2"/>
+      <c r="S220" s="2"/>
+      <c r="T220" s="2"/>
+      <c r="U220" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/rp/Excel/Effects_特效.xlsx
+++ b/rp/Excel/Effects_特效.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="500"/>
+    <workbookView windowWidth="24750" windowHeight="12060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="50">
   <si>
     <t>Int</t>
   </si>
@@ -56,6 +56,9 @@
     <t>0-Common
 1-Male
 2-FeMale</t>
+  </si>
+  <si>
+    <t>0|0|50|0|0|0|0.1|0.1|0.1</t>
   </si>
   <si>
     <t>0|0|0|0|0|0|1|1|1</t>
@@ -173,6 +176,9 @@
   </si>
   <si>
     <t>剪纸</t>
+  </si>
+  <si>
+    <t>0|0|150|0|0|0|1|1|1</t>
   </si>
 </sst>
 </file>
@@ -1363,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U214"/>
+  <dimension ref="A1:U220"/>
   <sheetFormatPr defaultColWidth="12.0666666666667" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="12.0666666666667" style="1"/>
@@ -1491,7 +1497,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="4">
-        <v>525387</v>
+        <v>681318</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -1522,10 +1528,10 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>501310</v>
+        <v>556585</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
@@ -1551,14 +1557,12 @@
       <c r="A7" s="4">
         <v>3</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="4">
+        <v>674918</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C7" s="4">
-        <v>57202</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="E7" s="4">
         <v>0</v>
@@ -1584,14 +1588,12 @@
       <c r="A8" s="4">
         <v>4</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="4">
-        <v>365194</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>13</v>
+        <v>565350</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
@@ -1617,14 +1619,12 @@
       <c r="A9" s="4">
         <v>5</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="4">
-        <v>28451</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>15</v>
+        <v>567138</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
@@ -1650,14 +1650,12 @@
       <c r="A10" s="4">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>16</v>
-      </c>
+      <c r="B10" s="2"/>
       <c r="C10" s="4">
-        <v>526080</v>
+        <v>567139</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4">
         <v>0</v>
@@ -1683,12 +1681,12 @@
       <c r="A11" s="4">
         <v>7</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="2"/>
       <c r="C11" s="4">
-        <v>464265</v>
+        <v>525387</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4">
         <v>0</v>
@@ -1714,12 +1712,12 @@
       <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="6"/>
+      <c r="B12" s="2"/>
       <c r="C12" s="4">
-        <v>266517</v>
+        <v>501310</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -1745,12 +1743,14 @@
       <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
+      <c r="B13" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C13" s="4">
-        <v>266518</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>17</v>
+        <v>57202</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
@@ -1776,12 +1776,14 @@
       <c r="A14" s="4">
         <v>10</v>
       </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C14" s="4">
-        <v>266519</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>17</v>
+        <v>365194</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -1807,12 +1809,14 @@
       <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="6"/>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C15" s="4">
-        <v>266520</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>28451</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -1838,12 +1842,14 @@
       <c r="A16" s="4">
         <v>12</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="C16" s="4">
-        <v>266521</v>
+        <v>526080</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1871,7 +1877,7 @@
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="4">
-        <v>439411</v>
+        <v>464265</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
@@ -1902,10 +1908,10 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="4">
-        <v>484531</v>
+        <v>266517</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -1933,10 +1939,10 @@
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="4">
-        <v>144088</v>
+        <v>266518</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -1964,10 +1970,10 @@
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="4">
-        <v>439415</v>
+        <v>266519</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" s="4">
         <v>0</v>
@@ -1995,10 +2001,10 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="4">
-        <v>144093</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>20</v>
+        <v>266520</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="E21" s="4">
         <v>0</v>
@@ -2026,10 +2032,10 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="4">
-        <v>326212</v>
+        <v>266521</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
@@ -2057,10 +2063,10 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="4">
-        <v>326224</v>
+        <v>439411</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -2088,10 +2094,10 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="4">
-        <v>383667</v>
+        <v>484531</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -2119,10 +2125,10 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="4">
-        <v>383676</v>
+        <v>144088</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -2150,10 +2156,10 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="4">
-        <v>386040</v>
+        <v>439415</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -2181,9 +2187,9 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="4">
-        <v>394667</v>
-      </c>
-      <c r="D27" s="2" t="s">
+        <v>144093</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E27" s="4">
@@ -2212,10 +2218,10 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="4">
-        <v>394678</v>
+        <v>326212</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -2241,14 +2247,12 @@
       <c r="A29" s="4">
         <v>25</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="6"/>
+      <c r="C29" s="4">
+        <v>326224</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C29" s="4">
-        <v>220840</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -2270,16 +2274,16 @@
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
     </row>
-    <row r="30" ht="17.25" spans="1:21">
+    <row r="30" spans="1:21">
       <c r="A30" s="4">
         <v>26</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="7">
-        <v>485354</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>24</v>
+      <c r="B30" s="6"/>
+      <c r="C30" s="4">
+        <v>383667</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
@@ -2305,14 +2309,12 @@
       <c r="A31" s="4">
         <v>27</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="6"/>
+      <c r="C31" s="4">
+        <v>383676</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C31" s="4">
-        <v>220841</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="E31" s="4">
         <v>0</v>
@@ -2338,14 +2340,12 @@
       <c r="A32" s="4">
         <v>28</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="6"/>
+      <c r="C32" s="4">
+        <v>386040</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C32" s="4">
-        <v>220842</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
@@ -2371,14 +2371,12 @@
       <c r="A33" s="4">
         <v>29</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="6"/>
+      <c r="C33" s="4">
+        <v>394667</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C33" s="4">
-        <v>220843</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="E33" s="4">
         <v>0</v>
@@ -2404,14 +2402,12 @@
       <c r="A34" s="4">
         <v>30</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="6"/>
+      <c r="C34" s="4">
+        <v>394678</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C34" s="4">
-        <v>220844</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -2437,14 +2433,14 @@
       <c r="A35" s="4">
         <v>31</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>22</v>
+      <c r="B35" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C35" s="4">
-        <v>220845</v>
+        <v>220840</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -2466,18 +2462,16 @@
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" ht="17.25" spans="1:21">
       <c r="A36" s="4">
         <v>32</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="4">
-        <v>220846</v>
+      <c r="B36" s="2"/>
+      <c r="C36" s="7">
+        <v>485354</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -2504,13 +2498,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C37" s="4">
-        <v>220847</v>
+        <v>220841</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -2537,13 +2531,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C38" s="4">
-        <v>220848</v>
+        <v>220842</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
@@ -2570,13 +2564,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C39" s="4">
-        <v>220849</v>
+        <v>220843</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -2603,13 +2597,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C40" s="4">
-        <v>220850</v>
+        <v>220844</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
@@ -2636,13 +2630,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="4">
-        <v>220851</v>
+        <v>220845</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
@@ -2669,13 +2663,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C42" s="4">
-        <v>220041</v>
+        <v>220846</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
@@ -2702,13 +2696,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C43" s="4">
-        <v>220469</v>
+        <v>220847</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
@@ -2735,13 +2729,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C44" s="4">
-        <v>31645</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>9</v>
+        <v>220848</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
@@ -2767,14 +2761,14 @@
       <c r="A45" s="4">
         <v>41</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>26</v>
+      <c r="B45" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C45" s="4">
-        <v>4366</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>9</v>
+        <v>220849</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -2801,13 +2795,13 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C46" s="4">
-        <v>4367</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>9</v>
+        <v>220850</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
@@ -2834,13 +2828,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C47" s="4">
-        <v>4368</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>9</v>
+        <v>220851</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E47" s="4">
         <v>0</v>
@@ -2866,12 +2860,14 @@
       <c r="A48" s="4">
         <v>44</v>
       </c>
-      <c r="B48" s="2"/>
+      <c r="B48" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="C48" s="4">
-        <v>144084</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>29</v>
+        <v>220041</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E48" s="4">
         <v>0</v>
@@ -2897,12 +2893,14 @@
       <c r="A49" s="4">
         <v>45</v>
       </c>
-      <c r="B49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="C49" s="4">
-        <v>146786</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>9</v>
+        <v>220469</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -2928,12 +2926,14 @@
       <c r="A50" s="4">
         <v>46</v>
       </c>
-      <c r="B50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C50" s="4">
-        <v>144083</v>
+        <v>31645</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -2960,13 +2960,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C51" s="4">
-        <v>32240</v>
+        <v>4366</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -2993,13 +2993,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C52" s="4">
-        <v>59956</v>
+        <v>4367</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -3026,13 +3026,13 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C53" s="4">
-        <v>73402</v>
+        <v>4368</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E53" s="4">
         <v>0</v>
@@ -3058,14 +3058,12 @@
       <c r="A54" s="4">
         <v>50</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="B54" s="2"/>
       <c r="C54" s="4">
-        <v>88762</v>
+        <v>144084</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E54" s="4">
         <v>0</v>
@@ -3091,14 +3089,12 @@
       <c r="A55" s="4">
         <v>51</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="B55" s="2"/>
       <c r="C55" s="4">
-        <v>88773</v>
+        <v>146786</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E55" s="4">
         <v>0</v>
@@ -3124,14 +3120,12 @@
       <c r="A56" s="4">
         <v>52</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="B56" s="2"/>
       <c r="C56" s="4">
-        <v>89073</v>
+        <v>144083</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E56" s="4">
         <v>0</v>
@@ -3158,13 +3152,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C57" s="4">
-        <v>89109</v>
+        <v>32240</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
@@ -3191,13 +3185,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C58" s="4">
-        <v>89111</v>
+        <v>59956</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E58" s="4">
         <v>0</v>
@@ -3224,13 +3218,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C59" s="4">
-        <v>89112</v>
+        <v>73402</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E59" s="4">
         <v>0</v>
@@ -3257,13 +3251,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C60" s="4">
-        <v>89122</v>
+        <v>88762</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E60" s="4">
         <v>0</v>
@@ -3290,13 +3284,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C61" s="4">
-        <v>113903</v>
+        <v>88773</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E61" s="4">
         <v>0</v>
@@ -3323,13 +3317,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C62" s="4">
-        <v>113913</v>
+        <v>89073</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E62" s="4">
         <v>0</v>
@@ -3356,13 +3350,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C63" s="4">
-        <v>113907</v>
+        <v>89109</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E63" s="4">
         <v>0</v>
@@ -3389,13 +3383,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C64" s="4">
-        <v>119917</v>
+        <v>89111</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E64" s="4">
         <v>0</v>
@@ -3422,13 +3416,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C65" s="4">
-        <v>130776</v>
+        <v>89112</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E65" s="4">
         <v>0</v>
@@ -3455,13 +3449,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C66" s="4">
-        <v>141655</v>
+        <v>89122</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E66" s="4">
         <v>0</v>
@@ -3488,13 +3482,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C67" s="4">
-        <v>141657</v>
+        <v>113903</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E67" s="4">
         <v>0</v>
@@ -3521,13 +3515,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C68" s="4">
-        <v>142753</v>
+        <v>113913</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E68" s="4">
         <v>0</v>
@@ -3554,13 +3548,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C69" s="4">
-        <v>142751</v>
+        <v>113907</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E69" s="4">
         <v>0</v>
@@ -3587,13 +3581,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C70" s="4">
-        <v>142951</v>
+        <v>119917</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E70" s="4">
         <v>0</v>
@@ -3620,13 +3614,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C71" s="4">
-        <v>156399</v>
+        <v>130776</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E71" s="4">
         <v>0</v>
@@ -3652,12 +3646,14 @@
       <c r="A72" s="4">
         <v>68</v>
       </c>
-      <c r="B72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="C72" s="4">
-        <v>157113</v>
+        <v>141655</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E72" s="4">
         <v>0</v>
@@ -3683,12 +3679,14 @@
       <c r="A73" s="4">
         <v>69</v>
       </c>
-      <c r="B73" s="2"/>
+      <c r="B73" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="C73" s="4">
-        <v>157118</v>
+        <v>141657</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E73" s="4">
         <v>0</v>
@@ -3714,12 +3712,14 @@
       <c r="A74" s="4">
         <v>70</v>
       </c>
-      <c r="B74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="C74" s="4">
-        <v>157119</v>
+        <v>142753</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E74" s="4">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C75" s="4">
-        <v>271322</v>
+        <v>142751</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75" s="4">
         <v>0</v>
@@ -3779,13 +3779,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C76" s="4">
-        <v>311092</v>
+        <v>142951</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" s="4">
         <v>0</v>
@@ -3812,13 +3812,13 @@
         <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C77" s="4">
-        <v>318586</v>
+        <v>156399</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E77" s="4">
         <v>0</v>
@@ -3846,10 +3846,10 @@
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="4">
-        <v>501294</v>
+        <v>157113</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E78" s="4">
         <v>0</v>
@@ -3875,14 +3875,12 @@
       <c r="A79" s="4">
         <v>75</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B79" s="2"/>
       <c r="C79" s="4">
-        <v>127013</v>
+        <v>157118</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E79" s="4">
         <v>0</v>
@@ -3910,10 +3908,10 @@
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="4">
-        <v>146328</v>
+        <v>157119</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E80" s="4">
         <v>0</v>
@@ -3939,12 +3937,14 @@
       <c r="A81" s="4">
         <v>77</v>
       </c>
-      <c r="B81" s="2"/>
+      <c r="B81" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="C81" s="4">
-        <v>146328</v>
+        <v>271322</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E81" s="4">
         <v>0</v>
@@ -3970,12 +3970,14 @@
       <c r="A82" s="4">
         <v>78</v>
       </c>
-      <c r="B82" s="2"/>
+      <c r="B82" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="C82" s="4">
-        <v>146753</v>
+        <v>311092</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E82" s="4">
         <v>0</v>
@@ -4005,10 +4007,10 @@
         <v>45</v>
       </c>
       <c r="C83" s="4">
-        <v>146754</v>
+        <v>318586</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E83" s="4">
         <v>0</v>
@@ -4034,14 +4036,12 @@
       <c r="A84" s="4">
         <v>80</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="4">
-        <v>144082</v>
+        <v>501294</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E84" s="4">
         <v>0</v>
@@ -4068,13 +4068,13 @@
         <v>81</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C85" s="4">
-        <v>361275</v>
+        <v>127013</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E85" s="4">
         <v>0</v>
@@ -4097,11 +4097,19 @@
       <c r="U85" s="2"/>
     </row>
     <row r="86" spans="1:21">
-      <c r="A86" s="2"/>
+      <c r="A86" s="4">
+        <v>82</v>
+      </c>
       <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
+      <c r="C86" s="4">
+        <v>146328</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="4">
+        <v>0</v>
+      </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -4120,11 +4128,19 @@
       <c r="U86" s="2"/>
     </row>
     <row r="87" spans="1:21">
-      <c r="A87" s="2"/>
+      <c r="A87" s="4">
+        <v>83</v>
+      </c>
       <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
+      <c r="C87" s="4">
+        <v>146328</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87" s="4">
+        <v>0</v>
+      </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -4143,11 +4159,19 @@
       <c r="U87" s="2"/>
     </row>
     <row r="88" spans="1:21">
-      <c r="A88" s="2"/>
+      <c r="A88" s="4">
+        <v>84</v>
+      </c>
       <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
+      <c r="C88" s="4">
+        <v>146753</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="4">
+        <v>0</v>
+      </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -4166,11 +4190,21 @@
       <c r="U88" s="2"/>
     </row>
     <row r="89" spans="1:21">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
+      <c r="A89" s="4">
+        <v>85</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C89" s="4">
+        <v>146754</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="4">
+        <v>0</v>
+      </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -4189,11 +4223,21 @@
       <c r="U89" s="2"/>
     </row>
     <row r="90" spans="1:21">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
+      <c r="A90" s="4">
+        <v>86</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C90" s="4">
+        <v>144082</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="4">
+        <v>0</v>
+      </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -4212,11 +4256,21 @@
       <c r="U90" s="2"/>
     </row>
     <row r="91" spans="1:21">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
+      <c r="A91" s="4">
+        <v>87</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C91" s="4">
+        <v>361275</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="4">
+        <v>0</v>
+      </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -4235,11 +4289,19 @@
       <c r="U91" s="2"/>
     </row>
     <row r="92" spans="1:21">
-      <c r="A92" s="2"/>
+      <c r="A92" s="4">
+        <v>88</v>
+      </c>
       <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
+      <c r="C92" s="4">
+        <v>558271</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E92" s="4">
+        <v>0</v>
+      </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -7063,6 +7125,144 @@
       <c r="T214" s="2"/>
       <c r="U214" s="2"/>
     </row>
+    <row r="215" spans="1:21">
+      <c r="A215" s="2"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+      <c r="E215" s="2"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
+      <c r="J215" s="2"/>
+      <c r="K215" s="2"/>
+      <c r="L215" s="2"/>
+      <c r="M215" s="2"/>
+      <c r="N215" s="2"/>
+      <c r="O215" s="2"/>
+      <c r="P215" s="2"/>
+      <c r="Q215" s="2"/>
+      <c r="R215" s="2"/>
+      <c r="S215" s="2"/>
+      <c r="T215" s="2"/>
+      <c r="U215" s="2"/>
+    </row>
+    <row r="216" spans="1:21">
+      <c r="A216" s="2"/>
+      <c r="B216" s="2"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
+      <c r="E216" s="2"/>
+      <c r="F216" s="2"/>
+      <c r="G216" s="2"/>
+      <c r="H216" s="2"/>
+      <c r="I216" s="2"/>
+      <c r="J216" s="2"/>
+      <c r="K216" s="2"/>
+      <c r="L216" s="2"/>
+      <c r="M216" s="2"/>
+      <c r="N216" s="2"/>
+      <c r="O216" s="2"/>
+      <c r="P216" s="2"/>
+      <c r="Q216" s="2"/>
+      <c r="R216" s="2"/>
+      <c r="S216" s="2"/>
+      <c r="T216" s="2"/>
+      <c r="U216" s="2"/>
+    </row>
+    <row r="217" spans="1:21">
+      <c r="A217" s="2"/>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
+      <c r="E217" s="2"/>
+      <c r="F217" s="2"/>
+      <c r="G217" s="2"/>
+      <c r="H217" s="2"/>
+      <c r="I217" s="2"/>
+      <c r="J217" s="2"/>
+      <c r="K217" s="2"/>
+      <c r="L217" s="2"/>
+      <c r="M217" s="2"/>
+      <c r="N217" s="2"/>
+      <c r="O217" s="2"/>
+      <c r="P217" s="2"/>
+      <c r="Q217" s="2"/>
+      <c r="R217" s="2"/>
+      <c r="S217" s="2"/>
+      <c r="T217" s="2"/>
+      <c r="U217" s="2"/>
+    </row>
+    <row r="218" spans="1:21">
+      <c r="A218" s="2"/>
+      <c r="B218" s="2"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
+      <c r="E218" s="2"/>
+      <c r="F218" s="2"/>
+      <c r="G218" s="2"/>
+      <c r="H218" s="2"/>
+      <c r="I218" s="2"/>
+      <c r="J218" s="2"/>
+      <c r="K218" s="2"/>
+      <c r="L218" s="2"/>
+      <c r="M218" s="2"/>
+      <c r="N218" s="2"/>
+      <c r="O218" s="2"/>
+      <c r="P218" s="2"/>
+      <c r="Q218" s="2"/>
+      <c r="R218" s="2"/>
+      <c r="S218" s="2"/>
+      <c r="T218" s="2"/>
+      <c r="U218" s="2"/>
+    </row>
+    <row r="219" spans="1:21">
+      <c r="A219" s="2"/>
+      <c r="B219" s="2"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
+      <c r="E219" s="2"/>
+      <c r="F219" s="2"/>
+      <c r="G219" s="2"/>
+      <c r="H219" s="2"/>
+      <c r="I219" s="2"/>
+      <c r="J219" s="2"/>
+      <c r="K219" s="2"/>
+      <c r="L219" s="2"/>
+      <c r="M219" s="2"/>
+      <c r="N219" s="2"/>
+      <c r="O219" s="2"/>
+      <c r="P219" s="2"/>
+      <c r="Q219" s="2"/>
+      <c r="R219" s="2"/>
+      <c r="S219" s="2"/>
+      <c r="T219" s="2"/>
+      <c r="U219" s="2"/>
+    </row>
+    <row r="220" spans="1:21">
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+      <c r="J220" s="2"/>
+      <c r="K220" s="2"/>
+      <c r="L220" s="2"/>
+      <c r="M220" s="2"/>
+      <c r="N220" s="2"/>
+      <c r="O220" s="2"/>
+      <c r="P220" s="2"/>
+      <c r="Q220" s="2"/>
+      <c r="R220" s="2"/>
+      <c r="S220" s="2"/>
+      <c r="T220" s="2"/>
+      <c r="U220" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
